--- a/idecba/pobreza_tasas.xlsx
+++ b/idecba/pobreza_tasas.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="16365" windowHeight="9825" tabRatio="845"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="10155" windowHeight="7365"/>
   </bookViews>
   <sheets>
     <sheet name="CV_AX15" sheetId="4" r:id="rId1"/>
@@ -33,7 +33,7 @@
     <definedName name="_xlnm.Print_Area" localSheetId="4">'2023'!$A$1:$I$20</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="13">'Ficha Técnica'!$A$1:$B$19</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="834" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="849" uniqueCount="87">
   <si>
     <t>Hogares</t>
   </si>
@@ -439,10 +439,10 @@
     <t>Distribución de hogares y personas por estrato de ingresos (%). Ciudad de Buenos Aires. 1er.trimestre de 2025/4to.trimestre de 2025</t>
   </si>
   <si>
-    <t>Distribución de hogares y personas por estrato de ingresos (%). Ciudad de Buenos Aires. 1er.trimestre de 2025/1er. trimestre de 2026</t>
+    <t>Distribución de hogares y personas por estrato de ingresos (%). Ciudad de Buenos Aires. 1er.trimestre de 2025/2do. trimestre de 2026</t>
   </si>
   <si>
-    <t>Distribución de hogares y personas por estrato de ingresos (%). Ciudad de Buenos Aires. 1er. trimestre de 2015/1er. trimestre de 2026</t>
+    <t>Distribución de hogares y personas por estrato de ingresos (%). Ciudad de Buenos Aires. 1er. trimestre de 2015/2do. trimestre de 2026</t>
   </si>
 </sst>
 </file>
@@ -3783,7 +3783,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="344">
+  <cellXfs count="345">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -4507,22 +4507,25 @@
       <alignment horizontal="right" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -4549,6 +4552,9 @@
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="36" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -4564,17 +4570,14 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="31" xfId="1430" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -6877,15 +6880,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="33.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="317" t="s">
+      <c r="A1" s="318" t="s">
         <v>86</v>
       </c>
-      <c r="B1" s="317"/>
-      <c r="C1" s="317"/>
-      <c r="D1" s="317"/>
-      <c r="E1" s="317"/>
-      <c r="F1" s="317"/>
-      <c r="G1" s="317"/>
+      <c r="B1" s="318"/>
+      <c r="C1" s="318"/>
+      <c r="D1" s="318"/>
+      <c r="E1" s="318"/>
+      <c r="F1" s="318"/>
+      <c r="G1" s="318"/>
     </row>
     <row r="2" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A2" s="253">
@@ -7060,41 +7063,41 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:33" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="324" t="s">
+      <c r="A1" s="325" t="s">
         <v>61</v>
       </c>
-      <c r="B1" s="324"/>
-      <c r="C1" s="324"/>
-      <c r="D1" s="324"/>
-      <c r="E1" s="324"/>
-      <c r="F1" s="324"/>
-      <c r="G1" s="324"/>
-      <c r="H1" s="324"/>
-      <c r="I1" s="324"/>
-      <c r="J1" s="324"/>
-      <c r="K1" s="324"/>
-      <c r="L1" s="324"/>
-      <c r="M1" s="324"/>
-      <c r="N1" s="324"/>
-      <c r="O1" s="324"/>
-      <c r="P1" s="324"/>
-      <c r="Q1" s="324"/>
-      <c r="R1" s="324"/>
-      <c r="S1" s="324"/>
-      <c r="T1" s="324"/>
-      <c r="U1" s="324"/>
-      <c r="V1" s="324"/>
-      <c r="W1" s="324"/>
-      <c r="X1" s="324"/>
-      <c r="Y1" s="324"/>
-      <c r="Z1" s="324"/>
-      <c r="AA1" s="324"/>
-      <c r="AB1" s="324"/>
-      <c r="AC1" s="324"/>
-      <c r="AD1" s="324"/>
-      <c r="AE1" s="324"/>
-      <c r="AF1" s="324"/>
-      <c r="AG1" s="324"/>
+      <c r="B1" s="325"/>
+      <c r="C1" s="325"/>
+      <c r="D1" s="325"/>
+      <c r="E1" s="325"/>
+      <c r="F1" s="325"/>
+      <c r="G1" s="325"/>
+      <c r="H1" s="325"/>
+      <c r="I1" s="325"/>
+      <c r="J1" s="325"/>
+      <c r="K1" s="325"/>
+      <c r="L1" s="325"/>
+      <c r="M1" s="325"/>
+      <c r="N1" s="325"/>
+      <c r="O1" s="325"/>
+      <c r="P1" s="325"/>
+      <c r="Q1" s="325"/>
+      <c r="R1" s="325"/>
+      <c r="S1" s="325"/>
+      <c r="T1" s="325"/>
+      <c r="U1" s="325"/>
+      <c r="V1" s="325"/>
+      <c r="W1" s="325"/>
+      <c r="X1" s="325"/>
+      <c r="Y1" s="325"/>
+      <c r="Z1" s="325"/>
+      <c r="AA1" s="325"/>
+      <c r="AB1" s="325"/>
+      <c r="AC1" s="325"/>
+      <c r="AD1" s="325"/>
+      <c r="AE1" s="325"/>
+      <c r="AF1" s="325"/>
+      <c r="AG1" s="325"/>
     </row>
     <row r="2" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A2" s="125"/>
@@ -7140,58 +7143,58 @@
       <c r="AG2" s="319"/>
     </row>
     <row r="3" spans="1:33" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A3" s="332"/>
-      <c r="B3" s="326" t="s">
+      <c r="A3" s="333"/>
+      <c r="B3" s="327" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="326"/>
-      <c r="D3" s="326"/>
-      <c r="E3" s="326"/>
-      <c r="F3" s="326" t="s">
+      <c r="C3" s="327"/>
+      <c r="D3" s="327"/>
+      <c r="E3" s="327"/>
+      <c r="F3" s="327" t="s">
         <v>1</v>
       </c>
-      <c r="G3" s="326"/>
-      <c r="H3" s="326"/>
-      <c r="I3" s="326"/>
-      <c r="J3" s="326" t="s">
+      <c r="G3" s="327"/>
+      <c r="H3" s="327"/>
+      <c r="I3" s="327"/>
+      <c r="J3" s="327" t="s">
         <v>0</v>
       </c>
-      <c r="K3" s="326"/>
-      <c r="L3" s="326"/>
-      <c r="M3" s="326"/>
-      <c r="N3" s="326" t="s">
+      <c r="K3" s="327"/>
+      <c r="L3" s="327"/>
+      <c r="M3" s="327"/>
+      <c r="N3" s="327" t="s">
         <v>1</v>
       </c>
-      <c r="O3" s="326"/>
-      <c r="P3" s="326"/>
+      <c r="O3" s="327"/>
+      <c r="P3" s="327"/>
       <c r="Q3" s="122"/>
-      <c r="R3" s="326" t="s">
+      <c r="R3" s="327" t="s">
         <v>0</v>
       </c>
-      <c r="S3" s="326"/>
-      <c r="T3" s="326"/>
-      <c r="U3" s="326"/>
-      <c r="V3" s="326" t="s">
+      <c r="S3" s="327"/>
+      <c r="T3" s="327"/>
+      <c r="U3" s="327"/>
+      <c r="V3" s="327" t="s">
         <v>1</v>
       </c>
-      <c r="W3" s="326"/>
-      <c r="X3" s="326"/>
+      <c r="W3" s="327"/>
+      <c r="X3" s="327"/>
       <c r="Y3" s="122"/>
-      <c r="Z3" s="326" t="s">
+      <c r="Z3" s="327" t="s">
         <v>0</v>
       </c>
-      <c r="AA3" s="326"/>
-      <c r="AB3" s="326"/>
-      <c r="AC3" s="326"/>
-      <c r="AD3" s="326" t="s">
+      <c r="AA3" s="327"/>
+      <c r="AB3" s="327"/>
+      <c r="AC3" s="327"/>
+      <c r="AD3" s="327" t="s">
         <v>1</v>
       </c>
-      <c r="AE3" s="326"/>
-      <c r="AF3" s="326"/>
+      <c r="AE3" s="327"/>
+      <c r="AF3" s="327"/>
       <c r="AG3" s="122"/>
     </row>
     <row r="4" spans="1:33" ht="24" x14ac:dyDescent="0.2">
-      <c r="A4" s="332"/>
+      <c r="A4" s="333"/>
       <c r="B4" s="123" t="s">
         <v>2</v>
       </c>
@@ -7910,41 +7913,41 @@
       <c r="AG13" s="166"/>
     </row>
     <row r="14" spans="1:33" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="323" t="s">
+      <c r="A14" s="324" t="s">
         <v>54</v>
       </c>
-      <c r="B14" s="323"/>
-      <c r="C14" s="323"/>
-      <c r="D14" s="323"/>
-      <c r="E14" s="323"/>
-      <c r="F14" s="323"/>
-      <c r="G14" s="323"/>
-      <c r="H14" s="323"/>
-      <c r="I14" s="323"/>
-      <c r="J14" s="323"/>
-      <c r="K14" s="323"/>
-      <c r="L14" s="323"/>
-      <c r="M14" s="323"/>
-      <c r="N14" s="323"/>
-      <c r="O14" s="323"/>
-      <c r="P14" s="323"/>
-      <c r="Q14" s="323"/>
-      <c r="R14" s="323"/>
-      <c r="S14" s="323"/>
-      <c r="T14" s="323"/>
-      <c r="U14" s="323"/>
-      <c r="V14" s="323"/>
-      <c r="W14" s="323"/>
-      <c r="X14" s="323"/>
-      <c r="Y14" s="323"/>
-      <c r="Z14" s="323"/>
-      <c r="AA14" s="323"/>
-      <c r="AB14" s="323"/>
-      <c r="AC14" s="323"/>
-      <c r="AD14" s="323"/>
-      <c r="AE14" s="323"/>
-      <c r="AF14" s="323"/>
-      <c r="AG14" s="323"/>
+      <c r="B14" s="324"/>
+      <c r="C14" s="324"/>
+      <c r="D14" s="324"/>
+      <c r="E14" s="324"/>
+      <c r="F14" s="324"/>
+      <c r="G14" s="324"/>
+      <c r="H14" s="324"/>
+      <c r="I14" s="324"/>
+      <c r="J14" s="324"/>
+      <c r="K14" s="324"/>
+      <c r="L14" s="324"/>
+      <c r="M14" s="324"/>
+      <c r="N14" s="324"/>
+      <c r="O14" s="324"/>
+      <c r="P14" s="324"/>
+      <c r="Q14" s="324"/>
+      <c r="R14" s="324"/>
+      <c r="S14" s="324"/>
+      <c r="T14" s="324"/>
+      <c r="U14" s="324"/>
+      <c r="V14" s="324"/>
+      <c r="W14" s="324"/>
+      <c r="X14" s="324"/>
+      <c r="Y14" s="324"/>
+      <c r="Z14" s="324"/>
+      <c r="AA14" s="324"/>
+      <c r="AB14" s="324"/>
+      <c r="AC14" s="324"/>
+      <c r="AD14" s="324"/>
+      <c r="AE14" s="324"/>
+      <c r="AF14" s="324"/>
+      <c r="AG14" s="324"/>
     </row>
     <row r="15" spans="1:33" ht="87.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="322" t="s">
@@ -7983,7 +7986,7 @@
       <c r="AF15" s="322"/>
       <c r="AG15" s="322"/>
     </row>
-    <row r="16" spans="1:33" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:33" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="322" t="s">
         <v>75</v>
       </c>
@@ -8259,6 +8262,14 @@
     </row>
   </sheetData>
   <mergeCells count="21">
+    <mergeCell ref="A1:AG1"/>
+    <mergeCell ref="A15:AG15"/>
+    <mergeCell ref="A16:AG16"/>
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="B3:E3"/>
+    <mergeCell ref="B2:I2"/>
+    <mergeCell ref="J2:Q2"/>
+    <mergeCell ref="V3:X3"/>
     <mergeCell ref="A18:AG18"/>
     <mergeCell ref="A19:AG19"/>
     <mergeCell ref="A20:AG20"/>
@@ -8272,14 +8283,6 @@
     <mergeCell ref="R2:Y2"/>
     <mergeCell ref="A17:AG17"/>
     <mergeCell ref="J3:M3"/>
-    <mergeCell ref="A1:AG1"/>
-    <mergeCell ref="A15:AG15"/>
-    <mergeCell ref="A16:AG16"/>
-    <mergeCell ref="A3:A4"/>
-    <mergeCell ref="B3:E3"/>
-    <mergeCell ref="B2:I2"/>
-    <mergeCell ref="J2:Q2"/>
-    <mergeCell ref="V3:X3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -8312,138 +8315,138 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:33" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="324" t="s">
+      <c r="A1" s="325" t="s">
         <v>55</v>
       </c>
-      <c r="B1" s="324"/>
-      <c r="C1" s="324"/>
-      <c r="D1" s="324"/>
-      <c r="E1" s="324"/>
-      <c r="F1" s="324"/>
-      <c r="G1" s="324"/>
-      <c r="H1" s="324"/>
-      <c r="I1" s="324"/>
-      <c r="J1" s="324"/>
-      <c r="K1" s="324"/>
-      <c r="L1" s="324"/>
-      <c r="M1" s="324"/>
-      <c r="N1" s="324"/>
-      <c r="O1" s="324"/>
-      <c r="P1" s="324"/>
-      <c r="Q1" s="324"/>
-      <c r="R1" s="324"/>
-      <c r="S1" s="324"/>
-      <c r="T1" s="324"/>
-      <c r="U1" s="324"/>
-      <c r="V1" s="324"/>
-      <c r="W1" s="324"/>
-      <c r="X1" s="324"/>
-      <c r="Y1" s="324"/>
-      <c r="Z1" s="324"/>
-      <c r="AA1" s="324"/>
-      <c r="AB1" s="324"/>
-      <c r="AC1" s="324"/>
-      <c r="AD1" s="324"/>
-      <c r="AE1" s="324"/>
-      <c r="AF1" s="324"/>
-      <c r="AG1" s="324"/>
+      <c r="B1" s="325"/>
+      <c r="C1" s="325"/>
+      <c r="D1" s="325"/>
+      <c r="E1" s="325"/>
+      <c r="F1" s="325"/>
+      <c r="G1" s="325"/>
+      <c r="H1" s="325"/>
+      <c r="I1" s="325"/>
+      <c r="J1" s="325"/>
+      <c r="K1" s="325"/>
+      <c r="L1" s="325"/>
+      <c r="M1" s="325"/>
+      <c r="N1" s="325"/>
+      <c r="O1" s="325"/>
+      <c r="P1" s="325"/>
+      <c r="Q1" s="325"/>
+      <c r="R1" s="325"/>
+      <c r="S1" s="325"/>
+      <c r="T1" s="325"/>
+      <c r="U1" s="325"/>
+      <c r="V1" s="325"/>
+      <c r="W1" s="325"/>
+      <c r="X1" s="325"/>
+      <c r="Y1" s="325"/>
+      <c r="Z1" s="325"/>
+      <c r="AA1" s="325"/>
+      <c r="AB1" s="325"/>
+      <c r="AC1" s="325"/>
+      <c r="AD1" s="325"/>
+      <c r="AE1" s="325"/>
+      <c r="AF1" s="325"/>
+      <c r="AG1" s="325"/>
     </row>
     <row r="2" spans="1:33" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A2" s="336"/>
-      <c r="B2" s="333" t="s">
+      <c r="A2" s="338"/>
+      <c r="B2" s="335" t="s">
         <v>50</v>
       </c>
-      <c r="C2" s="333"/>
-      <c r="D2" s="333"/>
-      <c r="E2" s="333"/>
-      <c r="F2" s="333"/>
-      <c r="G2" s="333"/>
-      <c r="H2" s="333"/>
+      <c r="C2" s="335"/>
+      <c r="D2" s="335"/>
+      <c r="E2" s="335"/>
+      <c r="F2" s="335"/>
+      <c r="G2" s="335"/>
+      <c r="H2" s="335"/>
       <c r="I2" s="71"/>
-      <c r="J2" s="334" t="s">
+      <c r="J2" s="336" t="s">
         <v>49</v>
       </c>
-      <c r="K2" s="333"/>
-      <c r="L2" s="333"/>
-      <c r="M2" s="333"/>
-      <c r="N2" s="333"/>
-      <c r="O2" s="333"/>
-      <c r="P2" s="333"/>
+      <c r="K2" s="335"/>
+      <c r="L2" s="335"/>
+      <c r="M2" s="335"/>
+      <c r="N2" s="335"/>
+      <c r="O2" s="335"/>
+      <c r="P2" s="335"/>
       <c r="Q2" s="71"/>
-      <c r="R2" s="334" t="s">
+      <c r="R2" s="336" t="s">
         <v>51</v>
       </c>
-      <c r="S2" s="333"/>
-      <c r="T2" s="333"/>
-      <c r="U2" s="333"/>
-      <c r="V2" s="333"/>
-      <c r="W2" s="333"/>
-      <c r="X2" s="333"/>
-      <c r="Y2" s="335"/>
-      <c r="Z2" s="334" t="s">
+      <c r="S2" s="335"/>
+      <c r="T2" s="335"/>
+      <c r="U2" s="335"/>
+      <c r="V2" s="335"/>
+      <c r="W2" s="335"/>
+      <c r="X2" s="335"/>
+      <c r="Y2" s="337"/>
+      <c r="Z2" s="336" t="s">
         <v>52</v>
       </c>
-      <c r="AA2" s="333"/>
-      <c r="AB2" s="333"/>
-      <c r="AC2" s="333"/>
-      <c r="AD2" s="333"/>
-      <c r="AE2" s="333"/>
-      <c r="AF2" s="333"/>
-      <c r="AG2" s="335"/>
+      <c r="AA2" s="335"/>
+      <c r="AB2" s="335"/>
+      <c r="AC2" s="335"/>
+      <c r="AD2" s="335"/>
+      <c r="AE2" s="335"/>
+      <c r="AF2" s="335"/>
+      <c r="AG2" s="337"/>
     </row>
     <row r="3" spans="1:33" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A3" s="337"/>
-      <c r="B3" s="333" t="s">
+      <c r="A3" s="339"/>
+      <c r="B3" s="335" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="333"/>
-      <c r="D3" s="333"/>
-      <c r="E3" s="333"/>
-      <c r="F3" s="333" t="s">
+      <c r="C3" s="335"/>
+      <c r="D3" s="335"/>
+      <c r="E3" s="335"/>
+      <c r="F3" s="335" t="s">
         <v>1</v>
       </c>
-      <c r="G3" s="333"/>
-      <c r="H3" s="333"/>
+      <c r="G3" s="335"/>
+      <c r="H3" s="335"/>
       <c r="I3" s="71"/>
-      <c r="J3" s="334" t="s">
+      <c r="J3" s="336" t="s">
         <v>0</v>
       </c>
-      <c r="K3" s="333"/>
-      <c r="L3" s="333"/>
-      <c r="M3" s="333"/>
-      <c r="N3" s="333" t="s">
+      <c r="K3" s="335"/>
+      <c r="L3" s="335"/>
+      <c r="M3" s="335"/>
+      <c r="N3" s="335" t="s">
         <v>1</v>
       </c>
-      <c r="O3" s="333"/>
-      <c r="P3" s="333"/>
+      <c r="O3" s="335"/>
+      <c r="P3" s="335"/>
       <c r="Q3" s="71"/>
-      <c r="R3" s="334" t="s">
+      <c r="R3" s="336" t="s">
         <v>0</v>
       </c>
-      <c r="S3" s="333"/>
-      <c r="T3" s="333"/>
-      <c r="U3" s="333"/>
-      <c r="V3" s="333" t="s">
+      <c r="S3" s="335"/>
+      <c r="T3" s="335"/>
+      <c r="U3" s="335"/>
+      <c r="V3" s="335" t="s">
         <v>1</v>
       </c>
-      <c r="W3" s="333"/>
-      <c r="X3" s="333"/>
+      <c r="W3" s="335"/>
+      <c r="X3" s="335"/>
       <c r="Y3" s="71"/>
-      <c r="Z3" s="334" t="s">
+      <c r="Z3" s="336" t="s">
         <v>0</v>
       </c>
-      <c r="AA3" s="333"/>
-      <c r="AB3" s="333"/>
-      <c r="AC3" s="333"/>
-      <c r="AD3" s="333" t="s">
+      <c r="AA3" s="335"/>
+      <c r="AB3" s="335"/>
+      <c r="AC3" s="335"/>
+      <c r="AD3" s="335" t="s">
         <v>1</v>
       </c>
-      <c r="AE3" s="333"/>
-      <c r="AF3" s="333"/>
+      <c r="AE3" s="335"/>
+      <c r="AF3" s="335"/>
       <c r="AG3" s="71"/>
     </row>
     <row r="4" spans="1:33" ht="24" x14ac:dyDescent="0.2">
-      <c r="A4" s="321"/>
+      <c r="A4" s="320"/>
       <c r="B4" s="110" t="s">
         <v>2</v>
       </c>
@@ -9191,41 +9194,41 @@
       <c r="AG13" s="59"/>
     </row>
     <row r="14" spans="1:33" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="323" t="s">
+      <c r="A14" s="324" t="s">
         <v>54</v>
       </c>
-      <c r="B14" s="323"/>
-      <c r="C14" s="323"/>
-      <c r="D14" s="323"/>
-      <c r="E14" s="323"/>
-      <c r="F14" s="323"/>
-      <c r="G14" s="323"/>
-      <c r="H14" s="323"/>
-      <c r="I14" s="323"/>
-      <c r="J14" s="323"/>
-      <c r="K14" s="323"/>
-      <c r="L14" s="323"/>
-      <c r="M14" s="323"/>
-      <c r="N14" s="323"/>
-      <c r="O14" s="323"/>
-      <c r="P14" s="323"/>
-      <c r="Q14" s="323"/>
-      <c r="R14" s="323"/>
-      <c r="S14" s="323"/>
-      <c r="T14" s="323"/>
-      <c r="U14" s="323"/>
-      <c r="V14" s="323"/>
-      <c r="W14" s="323"/>
-      <c r="X14" s="323"/>
-      <c r="Y14" s="323"/>
-      <c r="Z14" s="323"/>
-      <c r="AA14" s="323"/>
-      <c r="AB14" s="323"/>
-      <c r="AC14" s="323"/>
-      <c r="AD14" s="323"/>
-      <c r="AE14" s="323"/>
-      <c r="AF14" s="323"/>
-      <c r="AG14" s="323"/>
+      <c r="B14" s="324"/>
+      <c r="C14" s="324"/>
+      <c r="D14" s="324"/>
+      <c r="E14" s="324"/>
+      <c r="F14" s="324"/>
+      <c r="G14" s="324"/>
+      <c r="H14" s="324"/>
+      <c r="I14" s="324"/>
+      <c r="J14" s="324"/>
+      <c r="K14" s="324"/>
+      <c r="L14" s="324"/>
+      <c r="M14" s="324"/>
+      <c r="N14" s="324"/>
+      <c r="O14" s="324"/>
+      <c r="P14" s="324"/>
+      <c r="Q14" s="324"/>
+      <c r="R14" s="324"/>
+      <c r="S14" s="324"/>
+      <c r="T14" s="324"/>
+      <c r="U14" s="324"/>
+      <c r="V14" s="324"/>
+      <c r="W14" s="324"/>
+      <c r="X14" s="324"/>
+      <c r="Y14" s="324"/>
+      <c r="Z14" s="324"/>
+      <c r="AA14" s="324"/>
+      <c r="AB14" s="324"/>
+      <c r="AC14" s="324"/>
+      <c r="AD14" s="324"/>
+      <c r="AE14" s="324"/>
+      <c r="AF14" s="324"/>
+      <c r="AG14" s="324"/>
     </row>
     <row r="15" spans="1:33" ht="78" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="322" t="s">
@@ -9265,41 +9268,41 @@
       <c r="AG15" s="322"/>
     </row>
     <row r="16" spans="1:33" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="338" t="s">
+      <c r="A16" s="334" t="s">
         <v>76</v>
       </c>
-      <c r="B16" s="338"/>
-      <c r="C16" s="338"/>
-      <c r="D16" s="338"/>
-      <c r="E16" s="338"/>
-      <c r="F16" s="338"/>
-      <c r="G16" s="338"/>
-      <c r="H16" s="338"/>
-      <c r="I16" s="338"/>
-      <c r="J16" s="338"/>
-      <c r="K16" s="338"/>
-      <c r="L16" s="338"/>
-      <c r="M16" s="338"/>
-      <c r="N16" s="338"/>
-      <c r="O16" s="338"/>
-      <c r="P16" s="338"/>
-      <c r="Q16" s="338"/>
-      <c r="R16" s="338"/>
-      <c r="S16" s="338"/>
-      <c r="T16" s="338"/>
-      <c r="U16" s="338"/>
-      <c r="V16" s="338"/>
-      <c r="W16" s="338"/>
-      <c r="X16" s="338"/>
-      <c r="Y16" s="338"/>
-      <c r="Z16" s="338"/>
-      <c r="AA16" s="338"/>
-      <c r="AB16" s="338"/>
-      <c r="AC16" s="338"/>
-      <c r="AD16" s="338"/>
-      <c r="AE16" s="338"/>
-      <c r="AF16" s="338"/>
-      <c r="AG16" s="338"/>
+      <c r="B16" s="334"/>
+      <c r="C16" s="334"/>
+      <c r="D16" s="334"/>
+      <c r="E16" s="334"/>
+      <c r="F16" s="334"/>
+      <c r="G16" s="334"/>
+      <c r="H16" s="334"/>
+      <c r="I16" s="334"/>
+      <c r="J16" s="334"/>
+      <c r="K16" s="334"/>
+      <c r="L16" s="334"/>
+      <c r="M16" s="334"/>
+      <c r="N16" s="334"/>
+      <c r="O16" s="334"/>
+      <c r="P16" s="334"/>
+      <c r="Q16" s="334"/>
+      <c r="R16" s="334"/>
+      <c r="S16" s="334"/>
+      <c r="T16" s="334"/>
+      <c r="U16" s="334"/>
+      <c r="V16" s="334"/>
+      <c r="W16" s="334"/>
+      <c r="X16" s="334"/>
+      <c r="Y16" s="334"/>
+      <c r="Z16" s="334"/>
+      <c r="AA16" s="334"/>
+      <c r="AB16" s="334"/>
+      <c r="AC16" s="334"/>
+      <c r="AD16" s="334"/>
+      <c r="AE16" s="334"/>
+      <c r="AF16" s="334"/>
+      <c r="AG16" s="334"/>
     </row>
     <row r="17" spans="1:33" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="322" t="s">
@@ -9413,41 +9416,41 @@
       <c r="AG19" s="322"/>
     </row>
     <row r="20" spans="1:33" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="338" t="s">
+      <c r="A20" s="334" t="s">
         <v>68</v>
       </c>
-      <c r="B20" s="338"/>
-      <c r="C20" s="338"/>
-      <c r="D20" s="338"/>
-      <c r="E20" s="338"/>
-      <c r="F20" s="338"/>
-      <c r="G20" s="338"/>
-      <c r="H20" s="338"/>
-      <c r="I20" s="338"/>
-      <c r="J20" s="338"/>
-      <c r="K20" s="338"/>
-      <c r="L20" s="338"/>
-      <c r="M20" s="338"/>
-      <c r="N20" s="338"/>
-      <c r="O20" s="338"/>
-      <c r="P20" s="338"/>
-      <c r="Q20" s="338"/>
-      <c r="R20" s="338"/>
-      <c r="S20" s="338"/>
-      <c r="T20" s="338"/>
-      <c r="U20" s="338"/>
-      <c r="V20" s="338"/>
-      <c r="W20" s="338"/>
-      <c r="X20" s="338"/>
-      <c r="Y20" s="338"/>
-      <c r="Z20" s="338"/>
-      <c r="AA20" s="338"/>
-      <c r="AB20" s="338"/>
-      <c r="AC20" s="338"/>
-      <c r="AD20" s="338"/>
-      <c r="AE20" s="338"/>
-      <c r="AF20" s="338"/>
-      <c r="AG20" s="338"/>
+      <c r="B20" s="334"/>
+      <c r="C20" s="334"/>
+      <c r="D20" s="334"/>
+      <c r="E20" s="334"/>
+      <c r="F20" s="334"/>
+      <c r="G20" s="334"/>
+      <c r="H20" s="334"/>
+      <c r="I20" s="334"/>
+      <c r="J20" s="334"/>
+      <c r="K20" s="334"/>
+      <c r="L20" s="334"/>
+      <c r="M20" s="334"/>
+      <c r="N20" s="334"/>
+      <c r="O20" s="334"/>
+      <c r="P20" s="334"/>
+      <c r="Q20" s="334"/>
+      <c r="R20" s="334"/>
+      <c r="S20" s="334"/>
+      <c r="T20" s="334"/>
+      <c r="U20" s="334"/>
+      <c r="V20" s="334"/>
+      <c r="W20" s="334"/>
+      <c r="X20" s="334"/>
+      <c r="Y20" s="334"/>
+      <c r="Z20" s="334"/>
+      <c r="AA20" s="334"/>
+      <c r="AB20" s="334"/>
+      <c r="AC20" s="334"/>
+      <c r="AD20" s="334"/>
+      <c r="AE20" s="334"/>
+      <c r="AF20" s="334"/>
+      <c r="AG20" s="334"/>
     </row>
     <row r="21" spans="1:33" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A21" s="96"/>
@@ -9622,15 +9625,6 @@
     </row>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="A20:AG20"/>
-    <mergeCell ref="A16:AG16"/>
-    <mergeCell ref="V3:X3"/>
-    <mergeCell ref="A14:AG14"/>
-    <mergeCell ref="N3:P3"/>
-    <mergeCell ref="A18:AG18"/>
-    <mergeCell ref="A17:AG17"/>
-    <mergeCell ref="A19:AG19"/>
-    <mergeCell ref="A15:AG15"/>
     <mergeCell ref="B2:H2"/>
     <mergeCell ref="B3:E3"/>
     <mergeCell ref="A1:AG1"/>
@@ -9643,6 +9637,15 @@
     <mergeCell ref="J2:P2"/>
     <mergeCell ref="F3:H3"/>
     <mergeCell ref="R3:U3"/>
+    <mergeCell ref="A20:AG20"/>
+    <mergeCell ref="A16:AG16"/>
+    <mergeCell ref="V3:X3"/>
+    <mergeCell ref="A14:AG14"/>
+    <mergeCell ref="N3:P3"/>
+    <mergeCell ref="A18:AG18"/>
+    <mergeCell ref="A17:AG17"/>
+    <mergeCell ref="A19:AG19"/>
+    <mergeCell ref="A15:AG15"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -9682,117 +9685,117 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:36" x14ac:dyDescent="0.2">
-      <c r="A1" s="339" t="s">
+      <c r="A1" s="342" t="s">
         <v>36</v>
       </c>
-      <c r="B1" s="339"/>
-      <c r="C1" s="339"/>
-      <c r="D1" s="339"/>
-      <c r="E1" s="339"/>
-      <c r="F1" s="339"/>
-      <c r="G1" s="339"/>
-      <c r="H1" s="339"/>
-      <c r="I1" s="339"/>
-      <c r="J1" s="339"/>
-      <c r="K1" s="339"/>
-      <c r="L1" s="339"/>
-      <c r="M1" s="339"/>
-      <c r="N1" s="339"/>
-      <c r="O1" s="339"/>
+      <c r="B1" s="342"/>
+      <c r="C1" s="342"/>
+      <c r="D1" s="342"/>
+      <c r="E1" s="342"/>
+      <c r="F1" s="342"/>
+      <c r="G1" s="342"/>
+      <c r="H1" s="342"/>
+      <c r="I1" s="342"/>
+      <c r="J1" s="342"/>
+      <c r="K1" s="342"/>
+      <c r="L1" s="342"/>
+      <c r="M1" s="342"/>
+      <c r="N1" s="342"/>
+      <c r="O1" s="342"/>
       <c r="P1" s="68"/>
     </row>
     <row r="2" spans="1:36" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A2" s="336"/>
-      <c r="B2" s="333" t="s">
+      <c r="A2" s="338"/>
+      <c r="B2" s="335" t="s">
         <v>37</v>
       </c>
-      <c r="C2" s="333"/>
-      <c r="D2" s="333"/>
-      <c r="E2" s="333"/>
-      <c r="F2" s="333"/>
-      <c r="G2" s="333"/>
-      <c r="H2" s="333"/>
+      <c r="C2" s="335"/>
+      <c r="D2" s="335"/>
+      <c r="E2" s="335"/>
+      <c r="F2" s="335"/>
+      <c r="G2" s="335"/>
+      <c r="H2" s="335"/>
       <c r="I2" s="70"/>
-      <c r="J2" s="333" t="s">
+      <c r="J2" s="335" t="s">
         <v>38</v>
       </c>
-      <c r="K2" s="333"/>
-      <c r="L2" s="333"/>
-      <c r="M2" s="333"/>
-      <c r="N2" s="333"/>
-      <c r="O2" s="333"/>
+      <c r="K2" s="335"/>
+      <c r="L2" s="335"/>
+      <c r="M2" s="335"/>
+      <c r="N2" s="335"/>
+      <c r="O2" s="335"/>
       <c r="P2" s="69"/>
-      <c r="Q2" s="333" t="s">
+      <c r="Q2" s="335" t="s">
         <v>39</v>
       </c>
-      <c r="R2" s="333"/>
-      <c r="S2" s="333"/>
-      <c r="T2" s="333"/>
-      <c r="U2" s="333"/>
-      <c r="V2" s="333"/>
+      <c r="R2" s="335"/>
+      <c r="S2" s="335"/>
+      <c r="T2" s="335"/>
+      <c r="U2" s="335"/>
+      <c r="V2" s="335"/>
       <c r="W2" s="16"/>
-      <c r="X2" s="333" t="s">
+      <c r="X2" s="335" t="s">
         <v>40</v>
       </c>
-      <c r="Y2" s="333"/>
-      <c r="Z2" s="333"/>
-      <c r="AA2" s="336"/>
-      <c r="AB2" s="333"/>
-      <c r="AC2" s="333"/>
-      <c r="AD2" s="333"/>
+      <c r="Y2" s="335"/>
+      <c r="Z2" s="335"/>
+      <c r="AA2" s="338"/>
+      <c r="AB2" s="335"/>
+      <c r="AC2" s="335"/>
+      <c r="AD2" s="335"/>
       <c r="AE2" s="65"/>
     </row>
     <row r="3" spans="1:36" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A3" s="337"/>
-      <c r="B3" s="333" t="s">
+      <c r="A3" s="339"/>
+      <c r="B3" s="335" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="333"/>
-      <c r="D3" s="333"/>
-      <c r="E3" s="333"/>
-      <c r="F3" s="333" t="s">
+      <c r="C3" s="335"/>
+      <c r="D3" s="335"/>
+      <c r="E3" s="335"/>
+      <c r="F3" s="335" t="s">
         <v>1</v>
       </c>
-      <c r="G3" s="333"/>
-      <c r="H3" s="333"/>
+      <c r="G3" s="335"/>
+      <c r="H3" s="335"/>
       <c r="I3" s="71"/>
-      <c r="J3" s="333" t="s">
+      <c r="J3" s="335" t="s">
         <v>0</v>
       </c>
-      <c r="K3" s="333"/>
-      <c r="L3" s="335"/>
-      <c r="M3" s="333" t="s">
+      <c r="K3" s="335"/>
+      <c r="L3" s="337"/>
+      <c r="M3" s="335" t="s">
         <v>1</v>
       </c>
-      <c r="N3" s="333"/>
-      <c r="O3" s="333"/>
+      <c r="N3" s="335"/>
+      <c r="O3" s="335"/>
       <c r="P3" s="69"/>
-      <c r="Q3" s="334" t="s">
+      <c r="Q3" s="336" t="s">
         <v>0</v>
       </c>
-      <c r="R3" s="333"/>
-      <c r="S3" s="335"/>
-      <c r="T3" s="333" t="s">
+      <c r="R3" s="335"/>
+      <c r="S3" s="337"/>
+      <c r="T3" s="335" t="s">
         <v>1</v>
       </c>
-      <c r="U3" s="333"/>
-      <c r="V3" s="333"/>
+      <c r="U3" s="335"/>
+      <c r="V3" s="335"/>
       <c r="W3" s="16"/>
-      <c r="X3" s="334" t="s">
+      <c r="X3" s="336" t="s">
         <v>0</v>
       </c>
-      <c r="Y3" s="333"/>
-      <c r="Z3" s="333"/>
+      <c r="Y3" s="335"/>
+      <c r="Z3" s="335"/>
       <c r="AA3" s="72"/>
-      <c r="AB3" s="333" t="s">
+      <c r="AB3" s="335" t="s">
         <v>1</v>
       </c>
-      <c r="AC3" s="333"/>
-      <c r="AD3" s="333"/>
+      <c r="AC3" s="335"/>
+      <c r="AD3" s="335"/>
       <c r="AE3" s="65"/>
     </row>
     <row r="4" spans="1:36" ht="24" x14ac:dyDescent="0.2">
-      <c r="A4" s="321"/>
+      <c r="A4" s="320"/>
       <c r="B4" s="73" t="s">
         <v>2</v>
       </c>
@@ -10586,39 +10589,39 @@
       <c r="AE15" s="322"/>
     </row>
     <row r="16" spans="1:36" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="338" t="s">
+      <c r="A16" s="334" t="s">
         <v>76</v>
       </c>
-      <c r="B16" s="338"/>
-      <c r="C16" s="338"/>
-      <c r="D16" s="338"/>
-      <c r="E16" s="338"/>
-      <c r="F16" s="338"/>
-      <c r="G16" s="338"/>
-      <c r="H16" s="338"/>
-      <c r="I16" s="338"/>
-      <c r="J16" s="338"/>
-      <c r="K16" s="338"/>
-      <c r="L16" s="338"/>
-      <c r="M16" s="338"/>
-      <c r="N16" s="338"/>
-      <c r="O16" s="338"/>
-      <c r="P16" s="338"/>
-      <c r="Q16" s="338"/>
-      <c r="R16" s="338"/>
-      <c r="S16" s="338"/>
-      <c r="T16" s="338"/>
-      <c r="U16" s="338"/>
-      <c r="V16" s="338"/>
-      <c r="W16" s="338"/>
-      <c r="X16" s="338"/>
-      <c r="Y16" s="338"/>
-      <c r="Z16" s="338"/>
-      <c r="AA16" s="338"/>
-      <c r="AB16" s="338"/>
-      <c r="AC16" s="338"/>
-      <c r="AD16" s="338"/>
-      <c r="AE16" s="338"/>
+      <c r="B16" s="334"/>
+      <c r="C16" s="334"/>
+      <c r="D16" s="334"/>
+      <c r="E16" s="334"/>
+      <c r="F16" s="334"/>
+      <c r="G16" s="334"/>
+      <c r="H16" s="334"/>
+      <c r="I16" s="334"/>
+      <c r="J16" s="334"/>
+      <c r="K16" s="334"/>
+      <c r="L16" s="334"/>
+      <c r="M16" s="334"/>
+      <c r="N16" s="334"/>
+      <c r="O16" s="334"/>
+      <c r="P16" s="334"/>
+      <c r="Q16" s="334"/>
+      <c r="R16" s="334"/>
+      <c r="S16" s="334"/>
+      <c r="T16" s="334"/>
+      <c r="U16" s="334"/>
+      <c r="V16" s="334"/>
+      <c r="W16" s="334"/>
+      <c r="X16" s="334"/>
+      <c r="Y16" s="334"/>
+      <c r="Z16" s="334"/>
+      <c r="AA16" s="334"/>
+      <c r="AB16" s="334"/>
+      <c r="AC16" s="334"/>
+      <c r="AD16" s="334"/>
+      <c r="AE16" s="334"/>
     </row>
     <row r="17" spans="1:31" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="117" t="s">
@@ -10973,6 +10976,13 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="Q2:V2"/>
+    <mergeCell ref="X2:AD2"/>
+    <mergeCell ref="A1:O1"/>
+    <mergeCell ref="A2:A4"/>
+    <mergeCell ref="B2:H2"/>
+    <mergeCell ref="J2:O2"/>
+    <mergeCell ref="B3:E3"/>
     <mergeCell ref="A16:AE16"/>
     <mergeCell ref="F3:H3"/>
     <mergeCell ref="J3:L3"/>
@@ -10983,13 +10993,6 @@
     <mergeCell ref="X3:Z3"/>
     <mergeCell ref="AB3:AD3"/>
     <mergeCell ref="A15:AE15"/>
-    <mergeCell ref="Q2:V2"/>
-    <mergeCell ref="X2:AD2"/>
-    <mergeCell ref="A1:O1"/>
-    <mergeCell ref="A2:A4"/>
-    <mergeCell ref="B2:H2"/>
-    <mergeCell ref="J2:O2"/>
-    <mergeCell ref="B3:E3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -11024,130 +11027,130 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:33" x14ac:dyDescent="0.2">
-      <c r="A1" s="324" t="s">
+      <c r="A1" s="325" t="s">
         <v>53</v>
       </c>
-      <c r="B1" s="324"/>
-      <c r="C1" s="324"/>
-      <c r="D1" s="324"/>
-      <c r="E1" s="324"/>
-      <c r="F1" s="324"/>
-      <c r="G1" s="324"/>
-      <c r="H1" s="324"/>
-      <c r="I1" s="324"/>
-      <c r="J1" s="324"/>
-      <c r="K1" s="324"/>
-      <c r="L1" s="324"/>
-      <c r="M1" s="324"/>
-      <c r="N1" s="324"/>
-      <c r="O1" s="324"/>
-      <c r="P1" s="324"/>
-      <c r="Q1" s="324"/>
-      <c r="R1" s="324"/>
-      <c r="S1" s="324"/>
-      <c r="T1" s="324"/>
-      <c r="U1" s="324"/>
-      <c r="V1" s="324"/>
-      <c r="W1" s="324"/>
-      <c r="X1" s="324"/>
-      <c r="Y1" s="324"/>
+      <c r="B1" s="325"/>
+      <c r="C1" s="325"/>
+      <c r="D1" s="325"/>
+      <c r="E1" s="325"/>
+      <c r="F1" s="325"/>
+      <c r="G1" s="325"/>
+      <c r="H1" s="325"/>
+      <c r="I1" s="325"/>
+      <c r="J1" s="325"/>
+      <c r="K1" s="325"/>
+      <c r="L1" s="325"/>
+      <c r="M1" s="325"/>
+      <c r="N1" s="325"/>
+      <c r="O1" s="325"/>
+      <c r="P1" s="325"/>
+      <c r="Q1" s="325"/>
+      <c r="R1" s="325"/>
+      <c r="S1" s="325"/>
+      <c r="T1" s="325"/>
+      <c r="U1" s="325"/>
+      <c r="V1" s="325"/>
+      <c r="W1" s="325"/>
+      <c r="X1" s="325"/>
+      <c r="Y1" s="325"/>
     </row>
     <row r="2" spans="1:33" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A2" s="336"/>
-      <c r="B2" s="333" t="s">
+      <c r="A2" s="338"/>
+      <c r="B2" s="335" t="s">
         <v>50</v>
       </c>
-      <c r="C2" s="333"/>
-      <c r="D2" s="333"/>
-      <c r="E2" s="333"/>
-      <c r="F2" s="333"/>
-      <c r="G2" s="333"/>
-      <c r="H2" s="333"/>
+      <c r="C2" s="335"/>
+      <c r="D2" s="335"/>
+      <c r="E2" s="335"/>
+      <c r="F2" s="335"/>
+      <c r="G2" s="335"/>
+      <c r="H2" s="335"/>
       <c r="I2" s="71"/>
-      <c r="J2" s="334" t="s">
+      <c r="J2" s="336" t="s">
         <v>49</v>
       </c>
-      <c r="K2" s="333"/>
-      <c r="L2" s="333"/>
-      <c r="M2" s="333"/>
-      <c r="N2" s="333"/>
-      <c r="O2" s="333"/>
-      <c r="P2" s="333"/>
+      <c r="K2" s="335"/>
+      <c r="L2" s="335"/>
+      <c r="M2" s="335"/>
+      <c r="N2" s="335"/>
+      <c r="O2" s="335"/>
+      <c r="P2" s="335"/>
       <c r="Q2" s="71"/>
-      <c r="R2" s="334" t="s">
+      <c r="R2" s="336" t="s">
         <v>51</v>
       </c>
-      <c r="S2" s="333"/>
-      <c r="T2" s="333"/>
-      <c r="U2" s="333"/>
-      <c r="V2" s="333"/>
-      <c r="W2" s="333"/>
-      <c r="X2" s="333"/>
-      <c r="Y2" s="335"/>
-      <c r="Z2" s="334" t="s">
+      <c r="S2" s="335"/>
+      <c r="T2" s="335"/>
+      <c r="U2" s="335"/>
+      <c r="V2" s="335"/>
+      <c r="W2" s="335"/>
+      <c r="X2" s="335"/>
+      <c r="Y2" s="337"/>
+      <c r="Z2" s="336" t="s">
         <v>52</v>
       </c>
-      <c r="AA2" s="333"/>
-      <c r="AB2" s="333"/>
-      <c r="AC2" s="333"/>
-      <c r="AD2" s="333"/>
-      <c r="AE2" s="333"/>
-      <c r="AF2" s="333"/>
-      <c r="AG2" s="335"/>
+      <c r="AA2" s="335"/>
+      <c r="AB2" s="335"/>
+      <c r="AC2" s="335"/>
+      <c r="AD2" s="335"/>
+      <c r="AE2" s="335"/>
+      <c r="AF2" s="335"/>
+      <c r="AG2" s="337"/>
     </row>
     <row r="3" spans="1:33" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A3" s="337"/>
-      <c r="B3" s="333" t="s">
+      <c r="A3" s="339"/>
+      <c r="B3" s="335" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="333"/>
-      <c r="D3" s="333"/>
-      <c r="E3" s="333"/>
-      <c r="F3" s="333" t="s">
+      <c r="C3" s="335"/>
+      <c r="D3" s="335"/>
+      <c r="E3" s="335"/>
+      <c r="F3" s="335" t="s">
         <v>1</v>
       </c>
-      <c r="G3" s="333"/>
-      <c r="H3" s="333"/>
+      <c r="G3" s="335"/>
+      <c r="H3" s="335"/>
       <c r="I3" s="71"/>
-      <c r="J3" s="334" t="s">
+      <c r="J3" s="336" t="s">
         <v>0</v>
       </c>
-      <c r="K3" s="333"/>
-      <c r="L3" s="333"/>
-      <c r="M3" s="333"/>
-      <c r="N3" s="333" t="s">
+      <c r="K3" s="335"/>
+      <c r="L3" s="335"/>
+      <c r="M3" s="335"/>
+      <c r="N3" s="335" t="s">
         <v>1</v>
       </c>
-      <c r="O3" s="333"/>
-      <c r="P3" s="333"/>
+      <c r="O3" s="335"/>
+      <c r="P3" s="335"/>
       <c r="Q3" s="71"/>
-      <c r="R3" s="334" t="s">
+      <c r="R3" s="336" t="s">
         <v>0</v>
       </c>
-      <c r="S3" s="333"/>
-      <c r="T3" s="333"/>
-      <c r="U3" s="333"/>
-      <c r="V3" s="333" t="s">
+      <c r="S3" s="335"/>
+      <c r="T3" s="335"/>
+      <c r="U3" s="335"/>
+      <c r="V3" s="335" t="s">
         <v>1</v>
       </c>
-      <c r="W3" s="333"/>
-      <c r="X3" s="333"/>
+      <c r="W3" s="335"/>
+      <c r="X3" s="335"/>
       <c r="Y3" s="71"/>
-      <c r="Z3" s="334" t="s">
+      <c r="Z3" s="336" t="s">
         <v>0</v>
       </c>
-      <c r="AA3" s="333"/>
-      <c r="AB3" s="333"/>
-      <c r="AC3" s="333"/>
-      <c r="AD3" s="333" t="s">
+      <c r="AA3" s="335"/>
+      <c r="AB3" s="335"/>
+      <c r="AC3" s="335"/>
+      <c r="AD3" s="335" t="s">
         <v>1</v>
       </c>
-      <c r="AE3" s="333"/>
-      <c r="AF3" s="333"/>
+      <c r="AE3" s="335"/>
+      <c r="AF3" s="335"/>
       <c r="AG3" s="71"/>
     </row>
     <row r="4" spans="1:33" ht="24" x14ac:dyDescent="0.2">
-      <c r="A4" s="321"/>
+      <c r="A4" s="320"/>
       <c r="B4" s="110" t="s">
         <v>2</v>
       </c>
@@ -11871,41 +11874,41 @@
       <c r="AG13" s="59"/>
     </row>
     <row r="14" spans="1:33" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="323" t="s">
+      <c r="A14" s="324" t="s">
         <v>54</v>
       </c>
-      <c r="B14" s="323"/>
-      <c r="C14" s="323"/>
-      <c r="D14" s="323"/>
-      <c r="E14" s="323"/>
-      <c r="F14" s="323"/>
-      <c r="G14" s="323"/>
-      <c r="H14" s="323"/>
-      <c r="I14" s="323"/>
-      <c r="J14" s="323"/>
-      <c r="K14" s="323"/>
-      <c r="L14" s="323"/>
-      <c r="M14" s="323"/>
-      <c r="N14" s="323"/>
-      <c r="O14" s="323"/>
-      <c r="P14" s="323"/>
-      <c r="Q14" s="323"/>
-      <c r="R14" s="323"/>
-      <c r="S14" s="323"/>
-      <c r="T14" s="323"/>
-      <c r="U14" s="323"/>
-      <c r="V14" s="323"/>
-      <c r="W14" s="323"/>
-      <c r="X14" s="323"/>
-      <c r="Y14" s="323"/>
-      <c r="Z14" s="323"/>
-      <c r="AA14" s="323"/>
-      <c r="AB14" s="323"/>
-      <c r="AC14" s="323"/>
-      <c r="AD14" s="323"/>
-      <c r="AE14" s="323"/>
-      <c r="AF14" s="323"/>
-      <c r="AG14" s="323"/>
+      <c r="B14" s="324"/>
+      <c r="C14" s="324"/>
+      <c r="D14" s="324"/>
+      <c r="E14" s="324"/>
+      <c r="F14" s="324"/>
+      <c r="G14" s="324"/>
+      <c r="H14" s="324"/>
+      <c r="I14" s="324"/>
+      <c r="J14" s="324"/>
+      <c r="K14" s="324"/>
+      <c r="L14" s="324"/>
+      <c r="M14" s="324"/>
+      <c r="N14" s="324"/>
+      <c r="O14" s="324"/>
+      <c r="P14" s="324"/>
+      <c r="Q14" s="324"/>
+      <c r="R14" s="324"/>
+      <c r="S14" s="324"/>
+      <c r="T14" s="324"/>
+      <c r="U14" s="324"/>
+      <c r="V14" s="324"/>
+      <c r="W14" s="324"/>
+      <c r="X14" s="324"/>
+      <c r="Y14" s="324"/>
+      <c r="Z14" s="324"/>
+      <c r="AA14" s="324"/>
+      <c r="AB14" s="324"/>
+      <c r="AC14" s="324"/>
+      <c r="AD14" s="324"/>
+      <c r="AE14" s="324"/>
+      <c r="AF14" s="324"/>
+      <c r="AG14" s="324"/>
     </row>
     <row r="15" spans="1:33" ht="99.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="322" t="s">
@@ -11945,41 +11948,41 @@
       <c r="AG15" s="322"/>
     </row>
     <row r="16" spans="1:33" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="338" t="s">
+      <c r="A16" s="334" t="s">
         <v>77</v>
       </c>
-      <c r="B16" s="338"/>
-      <c r="C16" s="338"/>
-      <c r="D16" s="338"/>
-      <c r="E16" s="338"/>
-      <c r="F16" s="338"/>
-      <c r="G16" s="338"/>
-      <c r="H16" s="338"/>
-      <c r="I16" s="338"/>
-      <c r="J16" s="338"/>
-      <c r="K16" s="338"/>
-      <c r="L16" s="338"/>
-      <c r="M16" s="338"/>
-      <c r="N16" s="338"/>
-      <c r="O16" s="338"/>
-      <c r="P16" s="338"/>
-      <c r="Q16" s="338"/>
-      <c r="R16" s="338"/>
-      <c r="S16" s="338"/>
-      <c r="T16" s="338"/>
-      <c r="U16" s="338"/>
-      <c r="V16" s="338"/>
-      <c r="W16" s="338"/>
-      <c r="X16" s="338"/>
-      <c r="Y16" s="338"/>
-      <c r="Z16" s="338"/>
-      <c r="AA16" s="338"/>
-      <c r="AB16" s="338"/>
-      <c r="AC16" s="338"/>
-      <c r="AD16" s="338"/>
-      <c r="AE16" s="338"/>
-      <c r="AF16" s="338"/>
-      <c r="AG16" s="338"/>
+      <c r="B16" s="334"/>
+      <c r="C16" s="334"/>
+      <c r="D16" s="334"/>
+      <c r="E16" s="334"/>
+      <c r="F16" s="334"/>
+      <c r="G16" s="334"/>
+      <c r="H16" s="334"/>
+      <c r="I16" s="334"/>
+      <c r="J16" s="334"/>
+      <c r="K16" s="334"/>
+      <c r="L16" s="334"/>
+      <c r="M16" s="334"/>
+      <c r="N16" s="334"/>
+      <c r="O16" s="334"/>
+      <c r="P16" s="334"/>
+      <c r="Q16" s="334"/>
+      <c r="R16" s="334"/>
+      <c r="S16" s="334"/>
+      <c r="T16" s="334"/>
+      <c r="U16" s="334"/>
+      <c r="V16" s="334"/>
+      <c r="W16" s="334"/>
+      <c r="X16" s="334"/>
+      <c r="Y16" s="334"/>
+      <c r="Z16" s="334"/>
+      <c r="AA16" s="334"/>
+      <c r="AB16" s="334"/>
+      <c r="AC16" s="334"/>
+      <c r="AD16" s="334"/>
+      <c r="AE16" s="334"/>
+      <c r="AF16" s="334"/>
+      <c r="AG16" s="334"/>
     </row>
     <row r="17" spans="1:33" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="322" t="s">
@@ -12093,41 +12096,41 @@
       <c r="AG19" s="322"/>
     </row>
     <row r="20" spans="1:33" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="338" t="s">
+      <c r="A20" s="334" t="s">
         <v>68</v>
       </c>
-      <c r="B20" s="338"/>
-      <c r="C20" s="338"/>
-      <c r="D20" s="338"/>
-      <c r="E20" s="338"/>
-      <c r="F20" s="338"/>
-      <c r="G20" s="338"/>
-      <c r="H20" s="338"/>
-      <c r="I20" s="338"/>
-      <c r="J20" s="338"/>
-      <c r="K20" s="338"/>
-      <c r="L20" s="338"/>
-      <c r="M20" s="338"/>
-      <c r="N20" s="338"/>
-      <c r="O20" s="338"/>
-      <c r="P20" s="338"/>
-      <c r="Q20" s="338"/>
-      <c r="R20" s="338"/>
-      <c r="S20" s="338"/>
-      <c r="T20" s="338"/>
-      <c r="U20" s="338"/>
-      <c r="V20" s="338"/>
-      <c r="W20" s="338"/>
-      <c r="X20" s="338"/>
-      <c r="Y20" s="338"/>
-      <c r="Z20" s="338"/>
-      <c r="AA20" s="338"/>
-      <c r="AB20" s="338"/>
-      <c r="AC20" s="338"/>
-      <c r="AD20" s="338"/>
-      <c r="AE20" s="338"/>
-      <c r="AF20" s="338"/>
-      <c r="AG20" s="338"/>
+      <c r="B20" s="334"/>
+      <c r="C20" s="334"/>
+      <c r="D20" s="334"/>
+      <c r="E20" s="334"/>
+      <c r="F20" s="334"/>
+      <c r="G20" s="334"/>
+      <c r="H20" s="334"/>
+      <c r="I20" s="334"/>
+      <c r="J20" s="334"/>
+      <c r="K20" s="334"/>
+      <c r="L20" s="334"/>
+      <c r="M20" s="334"/>
+      <c r="N20" s="334"/>
+      <c r="O20" s="334"/>
+      <c r="P20" s="334"/>
+      <c r="Q20" s="334"/>
+      <c r="R20" s="334"/>
+      <c r="S20" s="334"/>
+      <c r="T20" s="334"/>
+      <c r="U20" s="334"/>
+      <c r="V20" s="334"/>
+      <c r="W20" s="334"/>
+      <c r="X20" s="334"/>
+      <c r="Y20" s="334"/>
+      <c r="Z20" s="334"/>
+      <c r="AA20" s="334"/>
+      <c r="AB20" s="334"/>
+      <c r="AC20" s="334"/>
+      <c r="AD20" s="334"/>
+      <c r="AE20" s="334"/>
+      <c r="AF20" s="334"/>
+      <c r="AG20" s="334"/>
     </row>
     <row r="21" spans="1:33" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A21" s="96"/>
@@ -12250,12 +12253,6 @@
     </row>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="A1:Y1"/>
-    <mergeCell ref="A2:A4"/>
-    <mergeCell ref="B2:H2"/>
-    <mergeCell ref="J2:P2"/>
-    <mergeCell ref="R2:Y2"/>
-    <mergeCell ref="B3:E3"/>
     <mergeCell ref="A20:AG20"/>
     <mergeCell ref="A17:AG17"/>
     <mergeCell ref="Z2:AG2"/>
@@ -12271,6 +12268,12 @@
     <mergeCell ref="A18:AG18"/>
     <mergeCell ref="N3:P3"/>
     <mergeCell ref="A19:AG19"/>
+    <mergeCell ref="A1:Y1"/>
+    <mergeCell ref="A2:A4"/>
+    <mergeCell ref="B2:H2"/>
+    <mergeCell ref="J2:P2"/>
+    <mergeCell ref="R2:Y2"/>
+    <mergeCell ref="B3:E3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -12287,10 +12290,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="342" t="s">
+      <c r="A1" s="343" t="s">
         <v>82</v>
       </c>
-      <c r="B1" s="343"/>
+      <c r="B1" s="344"/>
     </row>
     <row r="2" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A2" s="81" t="s">
@@ -12300,7 +12303,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="82" t="s">
         <v>16</v>
       </c>
@@ -12404,7 +12407,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="16" spans="1:2" ht="35.1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="82" t="s">
         <v>26</v>
       </c>
@@ -12412,7 +12415,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="17" spans="1:2" ht="35.1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:2" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="82" t="s">
         <v>48</v>
       </c>
@@ -12428,7 +12431,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="19" spans="1:2" ht="50.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" ht="45.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A19" s="92" t="s">
         <v>28</v>
       </c>
@@ -12447,7 +12450,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I24"/>
+  <dimension ref="A1:Q24"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="30.42578125" bestFit="1" customWidth="1"/>
@@ -12455,22 +12458,34 @@
     <col min="5" max="5" width="1.28515625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="1.28515625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="1.28515625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="1.28515625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="1.28515625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="1.28515625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="1.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="32.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="318" t="s">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A1" s="321" t="s">
         <v>85</v>
       </c>
-      <c r="B1" s="318"/>
-      <c r="C1" s="318"/>
-      <c r="D1" s="318"/>
-      <c r="E1" s="318"/>
-      <c r="F1" s="318"/>
-      <c r="G1" s="318"/>
-      <c r="H1" s="318"/>
-      <c r="I1" s="318"/>
-    </row>
-    <row r="2" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B1" s="321"/>
+      <c r="C1" s="321"/>
+      <c r="D1" s="321"/>
+      <c r="E1" s="321"/>
+      <c r="F1" s="321"/>
+      <c r="G1" s="321"/>
+      <c r="H1" s="321"/>
+      <c r="I1" s="321"/>
+      <c r="J1" s="321"/>
+      <c r="K1" s="321"/>
+      <c r="L1" s="321"/>
+      <c r="M1" s="321"/>
+      <c r="N1" s="321"/>
+      <c r="O1" s="321"/>
+      <c r="P1" s="321"/>
+      <c r="Q1" s="321"/>
+    </row>
+    <row r="2" spans="1:17" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="175"/>
       <c r="B2" s="319" t="s">
         <v>37</v>
@@ -12482,24 +12497,46 @@
       <c r="G2" s="319"/>
       <c r="H2" s="319"/>
       <c r="I2" s="319"/>
-    </row>
-    <row r="3" spans="1:9" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A3" s="320"/>
-      <c r="B3" s="321" t="s">
+      <c r="J2" s="319" t="s">
+        <v>38</v>
+      </c>
+      <c r="K2" s="319"/>
+      <c r="L2" s="319"/>
+      <c r="M2" s="319"/>
+      <c r="N2" s="319"/>
+      <c r="O2" s="319"/>
+      <c r="P2" s="319"/>
+      <c r="Q2" s="319"/>
+    </row>
+    <row r="3" spans="1:17" ht="13.5" x14ac:dyDescent="0.2">
+      <c r="A3" s="323"/>
+      <c r="B3" s="320" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="321"/>
-      <c r="D3" s="321"/>
-      <c r="E3" s="321"/>
-      <c r="F3" s="321" t="s">
+      <c r="C3" s="320"/>
+      <c r="D3" s="320"/>
+      <c r="E3" s="320"/>
+      <c r="F3" s="320" t="s">
         <v>1</v>
       </c>
-      <c r="G3" s="321"/>
-      <c r="H3" s="321"/>
+      <c r="G3" s="320"/>
+      <c r="H3" s="320"/>
       <c r="I3" s="274"/>
-    </row>
-    <row r="4" spans="1:9" ht="24" x14ac:dyDescent="0.2">
-      <c r="A4" s="320"/>
+      <c r="J3" s="320" t="s">
+        <v>0</v>
+      </c>
+      <c r="K3" s="320"/>
+      <c r="L3" s="320"/>
+      <c r="M3" s="320"/>
+      <c r="N3" s="320" t="s">
+        <v>1</v>
+      </c>
+      <c r="O3" s="320"/>
+      <c r="P3" s="320"/>
+      <c r="Q3" s="274"/>
+    </row>
+    <row r="4" spans="1:17" ht="24" x14ac:dyDescent="0.2">
+      <c r="A4" s="323"/>
       <c r="B4" s="236" t="s">
         <v>2</v>
       </c>
@@ -12516,8 +12553,24 @@
         <v>3</v>
       </c>
       <c r="I4" s="276"/>
-    </row>
-    <row r="5" spans="1:9" ht="13.5" x14ac:dyDescent="0.2">
+      <c r="J4" s="236" t="s">
+        <v>2</v>
+      </c>
+      <c r="K4" s="275"/>
+      <c r="L4" s="317" t="s">
+        <v>3</v>
+      </c>
+      <c r="M4" s="276"/>
+      <c r="N4" s="239" t="s">
+        <v>2</v>
+      </c>
+      <c r="O4" s="275"/>
+      <c r="P4" s="317" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q4" s="276"/>
+    </row>
+    <row r="5" spans="1:17" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A5" s="130" t="s">
         <v>4</v>
       </c>
@@ -12537,8 +12590,24 @@
         <v>3087000</v>
       </c>
       <c r="I5" s="132"/>
-    </row>
-    <row r="6" spans="1:9" ht="13.5" x14ac:dyDescent="0.2">
+      <c r="J5" s="260">
+        <v>100</v>
+      </c>
+      <c r="K5" s="277"/>
+      <c r="L5" s="242">
+        <v>1379000</v>
+      </c>
+      <c r="M5" s="198"/>
+      <c r="N5" s="30">
+        <v>99.999999999999986</v>
+      </c>
+      <c r="O5" s="198"/>
+      <c r="P5" s="242">
+        <v>3087000</v>
+      </c>
+      <c r="Q5" s="132"/>
+    </row>
+    <row r="6" spans="1:17" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A6" s="138" t="s">
         <v>5</v>
       </c>
@@ -12558,8 +12627,24 @@
         <v>651000</v>
       </c>
       <c r="I6" s="198"/>
-    </row>
-    <row r="7" spans="1:9" ht="13.5" x14ac:dyDescent="0.2">
+      <c r="J6" s="30">
+        <v>17.3</v>
+      </c>
+      <c r="K6" s="198"/>
+      <c r="L6" s="34">
+        <v>239000</v>
+      </c>
+      <c r="M6" s="95"/>
+      <c r="N6" s="30">
+        <v>21.9</v>
+      </c>
+      <c r="O6" s="198"/>
+      <c r="P6" s="34">
+        <v>675000</v>
+      </c>
+      <c r="Q6" s="198"/>
+    </row>
+    <row r="7" spans="1:17" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A7" s="144" t="s">
         <v>6</v>
       </c>
@@ -12587,8 +12672,32 @@
       <c r="I7" s="292" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="8" spans="1:9" ht="13.5" x14ac:dyDescent="0.2">
+      <c r="J7" s="206">
+        <v>4.5</v>
+      </c>
+      <c r="K7" s="278" t="s">
+        <v>7</v>
+      </c>
+      <c r="L7" s="224">
+        <v>63000</v>
+      </c>
+      <c r="M7" s="31" t="s">
+        <v>7</v>
+      </c>
+      <c r="N7" s="42">
+        <v>6.3</v>
+      </c>
+      <c r="O7" s="43" t="s">
+        <v>7</v>
+      </c>
+      <c r="P7" s="224">
+        <v>193000</v>
+      </c>
+      <c r="Q7" s="292" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A8" s="144" t="s">
         <v>56</v>
       </c>
@@ -12612,8 +12721,24 @@
       <c r="I8" s="292" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="9" spans="1:9" ht="13.5" x14ac:dyDescent="0.2">
+      <c r="J8" s="206">
+        <v>12.8</v>
+      </c>
+      <c r="K8" s="278"/>
+      <c r="L8" s="224">
+        <v>176000</v>
+      </c>
+      <c r="M8" s="31"/>
+      <c r="N8" s="42">
+        <v>15.6</v>
+      </c>
+      <c r="O8" s="43"/>
+      <c r="P8" s="224">
+        <v>482000</v>
+      </c>
+      <c r="Q8" s="292"/>
+    </row>
+    <row r="9" spans="1:17" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A9" s="138" t="s">
         <v>9</v>
       </c>
@@ -12632,8 +12757,23 @@
       <c r="H9" s="34">
         <v>2436000</v>
       </c>
-    </row>
-    <row r="10" spans="1:9" ht="13.5" x14ac:dyDescent="0.2">
+      <c r="J9" s="30">
+        <v>82.7</v>
+      </c>
+      <c r="K9" s="279"/>
+      <c r="L9" s="34">
+        <v>1140000</v>
+      </c>
+      <c r="M9" s="95"/>
+      <c r="N9" s="30">
+        <v>78.099999999999994</v>
+      </c>
+      <c r="O9" s="198"/>
+      <c r="P9" s="34">
+        <v>2412000</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A10" s="144" t="s">
         <v>10</v>
       </c>
@@ -12661,8 +12801,28 @@
       <c r="I10" s="292" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="11" spans="1:9" ht="13.5" x14ac:dyDescent="0.2">
+      <c r="J10" s="206">
+        <v>10.199999999999999</v>
+      </c>
+      <c r="K10" s="280"/>
+      <c r="L10" s="224">
+        <v>141000</v>
+      </c>
+      <c r="M10" s="31"/>
+      <c r="N10" s="42">
+        <v>10.9</v>
+      </c>
+      <c r="O10" s="43" t="s">
+        <v>7</v>
+      </c>
+      <c r="P10" s="224">
+        <v>337000</v>
+      </c>
+      <c r="Q10" s="292" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A11" s="144" t="s">
         <v>14</v>
       </c>
@@ -12690,8 +12850,28 @@
       <c r="I11" s="292" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="12" spans="1:9" ht="13.5" x14ac:dyDescent="0.2">
+      <c r="J11" s="206">
+        <v>8.4</v>
+      </c>
+      <c r="K11" s="278"/>
+      <c r="L11" s="224">
+        <v>116000</v>
+      </c>
+      <c r="M11" s="31"/>
+      <c r="N11" s="42">
+        <v>8.9</v>
+      </c>
+      <c r="O11" s="43" t="s">
+        <v>7</v>
+      </c>
+      <c r="P11" s="224">
+        <v>276000</v>
+      </c>
+      <c r="Q11" s="292" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A12" s="144" t="s">
         <v>62</v>
       </c>
@@ -12711,8 +12891,24 @@
         <v>1458000</v>
       </c>
       <c r="I12" s="292"/>
-    </row>
-    <row r="13" spans="1:9" ht="13.5" x14ac:dyDescent="0.2">
+      <c r="J12" s="206">
+        <v>53.5</v>
+      </c>
+      <c r="K12" s="278"/>
+      <c r="L12" s="224">
+        <v>737000</v>
+      </c>
+      <c r="M12" s="31"/>
+      <c r="N12" s="42">
+        <v>49.6</v>
+      </c>
+      <c r="O12" s="43"/>
+      <c r="P12" s="224">
+        <v>1532000</v>
+      </c>
+      <c r="Q12" s="292"/>
+    </row>
+    <row r="13" spans="1:17" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A13" s="144" t="s">
         <v>63</v>
       </c>
@@ -12734,8 +12930,24 @@
       <c r="I13" s="293" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="14" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="J13" s="265">
+        <v>10.6</v>
+      </c>
+      <c r="K13" s="281"/>
+      <c r="L13" s="251">
+        <v>146000</v>
+      </c>
+      <c r="M13" s="64"/>
+      <c r="N13" s="52">
+        <v>8.6999999999999993</v>
+      </c>
+      <c r="O13" s="57"/>
+      <c r="P13" s="251">
+        <v>267000</v>
+      </c>
+      <c r="Q13" s="293"/>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A14" s="316" t="s">
         <v>54</v>
       </c>
@@ -12748,7 +12960,7 @@
       <c r="H14" s="316"/>
       <c r="I14" s="316"/>
     </row>
-    <row r="15" spans="1:9" ht="152.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:17" ht="168.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="322" t="s">
         <v>64</v>
       </c>
@@ -12761,7 +12973,7 @@
       <c r="H15" s="322"/>
       <c r="I15" s="322"/>
     </row>
-    <row r="16" spans="1:9" ht="66" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:17" ht="67.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="322" t="s">
         <v>75</v>
       </c>
@@ -12774,7 +12986,7 @@
       <c r="H16" s="322"/>
       <c r="I16" s="322"/>
     </row>
-    <row r="17" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A17" s="322" t="s">
         <v>11</v>
       </c>
@@ -12787,7 +12999,7 @@
       <c r="H17" s="322"/>
       <c r="I17" s="322"/>
     </row>
-    <row r="18" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A18" s="322" t="s">
         <v>12</v>
       </c>
@@ -12813,7 +13025,7 @@
       <c r="H19" s="322"/>
       <c r="I19" s="322"/>
     </row>
-    <row r="20" spans="1:9" ht="40.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:9" ht="37.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="322" t="s">
         <v>79</v>
       </c>
@@ -12833,14 +13045,17 @@
       <c r="B24" s="1"/>
     </row>
   </sheetData>
-  <mergeCells count="11">
-    <mergeCell ref="A17:I17"/>
+  <mergeCells count="14">
     <mergeCell ref="A18:I18"/>
     <mergeCell ref="A19:I19"/>
     <mergeCell ref="A20:I20"/>
     <mergeCell ref="A15:I15"/>
     <mergeCell ref="A16:I16"/>
-    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="J2:Q2"/>
+    <mergeCell ref="J3:M3"/>
+    <mergeCell ref="N3:P3"/>
+    <mergeCell ref="A1:Q1"/>
+    <mergeCell ref="A17:I17"/>
     <mergeCell ref="B2:I2"/>
     <mergeCell ref="A3:A4"/>
     <mergeCell ref="B3:E3"/>
@@ -12876,41 +13091,41 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:33" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="318" t="s">
+      <c r="A1" s="321" t="s">
         <v>84</v>
       </c>
-      <c r="B1" s="318"/>
-      <c r="C1" s="318"/>
-      <c r="D1" s="318"/>
-      <c r="E1" s="318"/>
-      <c r="F1" s="318"/>
-      <c r="G1" s="318"/>
-      <c r="H1" s="318"/>
-      <c r="I1" s="318"/>
-      <c r="J1" s="318"/>
-      <c r="K1" s="318"/>
-      <c r="L1" s="318"/>
-      <c r="M1" s="318"/>
-      <c r="N1" s="318"/>
-      <c r="O1" s="318"/>
-      <c r="P1" s="318"/>
-      <c r="Q1" s="318"/>
-      <c r="R1" s="318"/>
-      <c r="S1" s="318"/>
-      <c r="T1" s="318"/>
-      <c r="U1" s="318"/>
-      <c r="V1" s="318"/>
-      <c r="W1" s="318"/>
-      <c r="X1" s="318"/>
-      <c r="Y1" s="318"/>
-      <c r="Z1" s="318"/>
-      <c r="AA1" s="318"/>
-      <c r="AB1" s="318"/>
-      <c r="AC1" s="318"/>
-      <c r="AD1" s="318"/>
-      <c r="AE1" s="318"/>
-      <c r="AF1" s="318"/>
-      <c r="AG1" s="318"/>
+      <c r="B1" s="321"/>
+      <c r="C1" s="321"/>
+      <c r="D1" s="321"/>
+      <c r="E1" s="321"/>
+      <c r="F1" s="321"/>
+      <c r="G1" s="321"/>
+      <c r="H1" s="321"/>
+      <c r="I1" s="321"/>
+      <c r="J1" s="321"/>
+      <c r="K1" s="321"/>
+      <c r="L1" s="321"/>
+      <c r="M1" s="321"/>
+      <c r="N1" s="321"/>
+      <c r="O1" s="321"/>
+      <c r="P1" s="321"/>
+      <c r="Q1" s="321"/>
+      <c r="R1" s="321"/>
+      <c r="S1" s="321"/>
+      <c r="T1" s="321"/>
+      <c r="U1" s="321"/>
+      <c r="V1" s="321"/>
+      <c r="W1" s="321"/>
+      <c r="X1" s="321"/>
+      <c r="Y1" s="321"/>
+      <c r="Z1" s="321"/>
+      <c r="AA1" s="321"/>
+      <c r="AB1" s="321"/>
+      <c r="AC1" s="321"/>
+      <c r="AD1" s="321"/>
+      <c r="AE1" s="321"/>
+      <c r="AF1" s="321"/>
+      <c r="AG1" s="321"/>
     </row>
     <row r="2" spans="1:33" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="175"/>
@@ -12956,58 +13171,58 @@
       <c r="AG2" s="319"/>
     </row>
     <row r="3" spans="1:33" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A3" s="320"/>
-      <c r="B3" s="321" t="s">
+      <c r="A3" s="323"/>
+      <c r="B3" s="320" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="321"/>
-      <c r="D3" s="321"/>
-      <c r="E3" s="321"/>
-      <c r="F3" s="321" t="s">
+      <c r="C3" s="320"/>
+      <c r="D3" s="320"/>
+      <c r="E3" s="320"/>
+      <c r="F3" s="320" t="s">
         <v>1</v>
       </c>
-      <c r="G3" s="321"/>
-      <c r="H3" s="321"/>
+      <c r="G3" s="320"/>
+      <c r="H3" s="320"/>
       <c r="I3" s="274"/>
-      <c r="J3" s="321" t="s">
+      <c r="J3" s="320" t="s">
         <v>0</v>
       </c>
-      <c r="K3" s="321"/>
-      <c r="L3" s="321"/>
-      <c r="M3" s="321"/>
-      <c r="N3" s="321" t="s">
+      <c r="K3" s="320"/>
+      <c r="L3" s="320"/>
+      <c r="M3" s="320"/>
+      <c r="N3" s="320" t="s">
         <v>1</v>
       </c>
-      <c r="O3" s="321"/>
-      <c r="P3" s="321"/>
+      <c r="O3" s="320"/>
+      <c r="P3" s="320"/>
       <c r="Q3" s="274"/>
-      <c r="R3" s="321" t="s">
+      <c r="R3" s="320" t="s">
         <v>0</v>
       </c>
-      <c r="S3" s="321"/>
-      <c r="T3" s="321"/>
-      <c r="U3" s="321"/>
-      <c r="V3" s="321" t="s">
+      <c r="S3" s="320"/>
+      <c r="T3" s="320"/>
+      <c r="U3" s="320"/>
+      <c r="V3" s="320" t="s">
         <v>1</v>
       </c>
-      <c r="W3" s="321"/>
-      <c r="X3" s="321"/>
+      <c r="W3" s="320"/>
+      <c r="X3" s="320"/>
       <c r="Y3" s="274"/>
-      <c r="Z3" s="321" t="s">
+      <c r="Z3" s="320" t="s">
         <v>0</v>
       </c>
-      <c r="AA3" s="321"/>
-      <c r="AB3" s="321"/>
-      <c r="AC3" s="321"/>
-      <c r="AD3" s="321" t="s">
+      <c r="AA3" s="320"/>
+      <c r="AB3" s="320"/>
+      <c r="AC3" s="320"/>
+      <c r="AD3" s="320" t="s">
         <v>1</v>
       </c>
-      <c r="AE3" s="321"/>
-      <c r="AF3" s="321"/>
+      <c r="AE3" s="320"/>
+      <c r="AF3" s="320"/>
       <c r="AG3" s="274"/>
     </row>
     <row r="4" spans="1:33" ht="24" x14ac:dyDescent="0.2">
-      <c r="A4" s="320"/>
+      <c r="A4" s="323"/>
       <c r="B4" s="236" t="s">
         <v>2</v>
       </c>
@@ -13783,7 +13998,7 @@
       <c r="H14" s="316"/>
       <c r="I14" s="316"/>
     </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:33" ht="161.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="322" t="s">
         <v>64</v>
       </c>
@@ -13796,7 +14011,7 @@
       <c r="H15" s="322"/>
       <c r="I15" s="322"/>
     </row>
-    <row r="16" spans="1:33" ht="41.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:33" ht="64.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="322" t="s">
         <v>75</v>
       </c>
@@ -13869,12 +14084,6 @@
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="A19:I19"/>
-    <mergeCell ref="A20:I20"/>
-    <mergeCell ref="A15:I15"/>
-    <mergeCell ref="A16:I16"/>
-    <mergeCell ref="A17:I17"/>
-    <mergeCell ref="A18:I18"/>
     <mergeCell ref="F3:H3"/>
     <mergeCell ref="Z2:AG2"/>
     <mergeCell ref="Z3:AC3"/>
@@ -13889,6 +14098,12 @@
     <mergeCell ref="B2:I2"/>
     <mergeCell ref="A3:A4"/>
     <mergeCell ref="B3:E3"/>
+    <mergeCell ref="A19:I19"/>
+    <mergeCell ref="A20:I20"/>
+    <mergeCell ref="A15:I15"/>
+    <mergeCell ref="A16:I16"/>
+    <mergeCell ref="A17:I17"/>
+    <mergeCell ref="A18:I18"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -13924,41 +14139,41 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:33" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="318" t="s">
+      <c r="A1" s="321" t="s">
         <v>81</v>
       </c>
-      <c r="B1" s="318"/>
-      <c r="C1" s="318"/>
-      <c r="D1" s="318"/>
-      <c r="E1" s="318"/>
-      <c r="F1" s="318"/>
-      <c r="G1" s="318"/>
-      <c r="H1" s="318"/>
-      <c r="I1" s="318"/>
-      <c r="J1" s="318"/>
-      <c r="K1" s="318"/>
-      <c r="L1" s="318"/>
-      <c r="M1" s="318"/>
-      <c r="N1" s="318"/>
-      <c r="O1" s="318"/>
-      <c r="P1" s="318"/>
-      <c r="Q1" s="318"/>
-      <c r="R1" s="318"/>
-      <c r="S1" s="318"/>
-      <c r="T1" s="318"/>
-      <c r="U1" s="318"/>
-      <c r="V1" s="318"/>
-      <c r="W1" s="318"/>
-      <c r="X1" s="318"/>
-      <c r="Y1" s="318"/>
-      <c r="Z1" s="318"/>
-      <c r="AA1" s="318"/>
-      <c r="AB1" s="318"/>
-      <c r="AC1" s="318"/>
-      <c r="AD1" s="318"/>
-      <c r="AE1" s="318"/>
-      <c r="AF1" s="318"/>
-      <c r="AG1" s="318"/>
+      <c r="B1" s="321"/>
+      <c r="C1" s="321"/>
+      <c r="D1" s="321"/>
+      <c r="E1" s="321"/>
+      <c r="F1" s="321"/>
+      <c r="G1" s="321"/>
+      <c r="H1" s="321"/>
+      <c r="I1" s="321"/>
+      <c r="J1" s="321"/>
+      <c r="K1" s="321"/>
+      <c r="L1" s="321"/>
+      <c r="M1" s="321"/>
+      <c r="N1" s="321"/>
+      <c r="O1" s="321"/>
+      <c r="P1" s="321"/>
+      <c r="Q1" s="321"/>
+      <c r="R1" s="321"/>
+      <c r="S1" s="321"/>
+      <c r="T1" s="321"/>
+      <c r="U1" s="321"/>
+      <c r="V1" s="321"/>
+      <c r="W1" s="321"/>
+      <c r="X1" s="321"/>
+      <c r="Y1" s="321"/>
+      <c r="Z1" s="321"/>
+      <c r="AA1" s="321"/>
+      <c r="AB1" s="321"/>
+      <c r="AC1" s="321"/>
+      <c r="AD1" s="321"/>
+      <c r="AE1" s="321"/>
+      <c r="AF1" s="321"/>
+      <c r="AG1" s="321"/>
     </row>
     <row r="2" spans="1:33" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="175"/>
@@ -14004,30 +14219,30 @@
       <c r="AG2" s="319"/>
     </row>
     <row r="3" spans="1:33" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A3" s="320"/>
-      <c r="B3" s="321" t="s">
+      <c r="A3" s="323"/>
+      <c r="B3" s="320" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="321"/>
-      <c r="D3" s="321"/>
-      <c r="E3" s="321"/>
-      <c r="F3" s="321" t="s">
+      <c r="C3" s="320"/>
+      <c r="D3" s="320"/>
+      <c r="E3" s="320"/>
+      <c r="F3" s="320" t="s">
         <v>1</v>
       </c>
-      <c r="G3" s="321"/>
-      <c r="H3" s="321"/>
+      <c r="G3" s="320"/>
+      <c r="H3" s="320"/>
       <c r="I3" s="274"/>
-      <c r="J3" s="321" t="s">
+      <c r="J3" s="320" t="s">
         <v>0</v>
       </c>
-      <c r="K3" s="321"/>
-      <c r="L3" s="321"/>
-      <c r="M3" s="321"/>
-      <c r="N3" s="321" t="s">
+      <c r="K3" s="320"/>
+      <c r="L3" s="320"/>
+      <c r="M3" s="320"/>
+      <c r="N3" s="320" t="s">
         <v>1</v>
       </c>
-      <c r="O3" s="321"/>
-      <c r="P3" s="321"/>
+      <c r="O3" s="320"/>
+      <c r="P3" s="320"/>
       <c r="Q3" s="274"/>
       <c r="R3" s="236" t="s">
         <v>0</v>
@@ -14055,7 +14270,7 @@
       <c r="AG3" s="276"/>
     </row>
     <row r="4" spans="1:33" ht="24" x14ac:dyDescent="0.2">
-      <c r="A4" s="320"/>
+      <c r="A4" s="323"/>
       <c r="B4" s="236" t="s">
         <v>2</v>
       </c>
@@ -14781,20 +14996,20 @@
       </c>
       <c r="AG13" s="285"/>
     </row>
-    <row r="14" spans="1:33" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="323" t="s">
+    <row r="14" spans="1:33" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="324" t="s">
         <v>54</v>
       </c>
-      <c r="B14" s="323"/>
-      <c r="C14" s="323"/>
-      <c r="D14" s="323"/>
-      <c r="E14" s="323"/>
-      <c r="F14" s="323"/>
-      <c r="G14" s="323"/>
-      <c r="H14" s="323"/>
-      <c r="I14" s="323"/>
-    </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="B14" s="324"/>
+      <c r="C14" s="324"/>
+      <c r="D14" s="324"/>
+      <c r="E14" s="324"/>
+      <c r="F14" s="324"/>
+      <c r="G14" s="324"/>
+      <c r="H14" s="324"/>
+      <c r="I14" s="324"/>
+    </row>
+    <row r="15" spans="1:33" ht="162.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="322" t="s">
         <v>64</v>
       </c>
@@ -14807,7 +15022,7 @@
       <c r="H15" s="322"/>
       <c r="I15" s="322"/>
     </row>
-    <row r="16" spans="1:33" ht="52.15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:33" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="322" t="s">
         <v>75</v>
       </c>
@@ -14859,7 +15074,7 @@
       <c r="H19" s="322"/>
       <c r="I19" s="322"/>
     </row>
-    <row r="20" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:10" ht="40.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="322" t="s">
         <v>79</v>
       </c>
@@ -14882,12 +15097,6 @@
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="J2:Q2"/>
-    <mergeCell ref="J3:M3"/>
-    <mergeCell ref="N3:P3"/>
-    <mergeCell ref="Z2:AG2"/>
-    <mergeCell ref="A1:AG1"/>
-    <mergeCell ref="R2:Y2"/>
     <mergeCell ref="A20:I20"/>
     <mergeCell ref="B2:I2"/>
     <mergeCell ref="A3:A4"/>
@@ -14899,6 +15108,12 @@
     <mergeCell ref="A17:I17"/>
     <mergeCell ref="A18:I18"/>
     <mergeCell ref="A19:I19"/>
+    <mergeCell ref="J2:Q2"/>
+    <mergeCell ref="J3:M3"/>
+    <mergeCell ref="N3:P3"/>
+    <mergeCell ref="Z2:AG2"/>
+    <mergeCell ref="A1:AG1"/>
+    <mergeCell ref="R2:Y2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -14943,41 +15158,41 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:33" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="324" t="s">
+      <c r="A1" s="325" t="s">
         <v>78</v>
       </c>
-      <c r="B1" s="324"/>
-      <c r="C1" s="324"/>
-      <c r="D1" s="324"/>
-      <c r="E1" s="324"/>
-      <c r="F1" s="324"/>
-      <c r="G1" s="324"/>
-      <c r="H1" s="324"/>
-      <c r="I1" s="324"/>
-      <c r="J1" s="324"/>
-      <c r="K1" s="324"/>
-      <c r="L1" s="324"/>
-      <c r="M1" s="324"/>
-      <c r="N1" s="324"/>
-      <c r="O1" s="324"/>
-      <c r="P1" s="324"/>
-      <c r="Q1" s="324"/>
-      <c r="R1" s="324"/>
-      <c r="S1" s="324"/>
-      <c r="T1" s="324"/>
-      <c r="U1" s="324"/>
-      <c r="V1" s="324"/>
-      <c r="W1" s="324"/>
-      <c r="X1" s="324"/>
-      <c r="Y1" s="324"/>
-      <c r="Z1" s="324"/>
-      <c r="AA1" s="324"/>
-      <c r="AB1" s="324"/>
-      <c r="AC1" s="324"/>
-      <c r="AD1" s="324"/>
-      <c r="AE1" s="324"/>
-      <c r="AF1" s="324"/>
-      <c r="AG1" s="324"/>
+      <c r="B1" s="325"/>
+      <c r="C1" s="325"/>
+      <c r="D1" s="325"/>
+      <c r="E1" s="325"/>
+      <c r="F1" s="325"/>
+      <c r="G1" s="325"/>
+      <c r="H1" s="325"/>
+      <c r="I1" s="325"/>
+      <c r="J1" s="325"/>
+      <c r="K1" s="325"/>
+      <c r="L1" s="325"/>
+      <c r="M1" s="325"/>
+      <c r="N1" s="325"/>
+      <c r="O1" s="325"/>
+      <c r="P1" s="325"/>
+      <c r="Q1" s="325"/>
+      <c r="R1" s="325"/>
+      <c r="S1" s="325"/>
+      <c r="T1" s="325"/>
+      <c r="U1" s="325"/>
+      <c r="V1" s="325"/>
+      <c r="W1" s="325"/>
+      <c r="X1" s="325"/>
+      <c r="Y1" s="325"/>
+      <c r="Z1" s="325"/>
+      <c r="AA1" s="325"/>
+      <c r="AB1" s="325"/>
+      <c r="AC1" s="325"/>
+      <c r="AD1" s="325"/>
+      <c r="AE1" s="325"/>
+      <c r="AF1" s="325"/>
+      <c r="AG1" s="325"/>
     </row>
     <row r="2" spans="1:33" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="175"/>
@@ -15023,58 +15238,58 @@
       <c r="AG2" s="319"/>
     </row>
     <row r="3" spans="1:33" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A3" s="320"/>
-      <c r="B3" s="321" t="s">
+      <c r="A3" s="323"/>
+      <c r="B3" s="320" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="321"/>
-      <c r="D3" s="321"/>
-      <c r="E3" s="321"/>
-      <c r="F3" s="321" t="s">
+      <c r="C3" s="320"/>
+      <c r="D3" s="320"/>
+      <c r="E3" s="320"/>
+      <c r="F3" s="320" t="s">
         <v>1</v>
       </c>
-      <c r="G3" s="321"/>
-      <c r="H3" s="321"/>
+      <c r="G3" s="320"/>
+      <c r="H3" s="320"/>
       <c r="I3" s="274"/>
-      <c r="J3" s="321" t="s">
+      <c r="J3" s="320" t="s">
         <v>0</v>
       </c>
-      <c r="K3" s="321"/>
-      <c r="L3" s="321"/>
-      <c r="M3" s="321"/>
-      <c r="N3" s="321" t="s">
+      <c r="K3" s="320"/>
+      <c r="L3" s="320"/>
+      <c r="M3" s="320"/>
+      <c r="N3" s="320" t="s">
         <v>1</v>
       </c>
-      <c r="O3" s="321"/>
-      <c r="P3" s="321"/>
+      <c r="O3" s="320"/>
+      <c r="P3" s="320"/>
       <c r="Q3" s="235"/>
-      <c r="R3" s="321" t="s">
+      <c r="R3" s="320" t="s">
         <v>0</v>
       </c>
-      <c r="S3" s="321"/>
-      <c r="T3" s="321"/>
-      <c r="U3" s="321"/>
-      <c r="V3" s="321" t="s">
+      <c r="S3" s="320"/>
+      <c r="T3" s="320"/>
+      <c r="U3" s="320"/>
+      <c r="V3" s="320" t="s">
         <v>1</v>
       </c>
-      <c r="W3" s="321"/>
-      <c r="X3" s="321"/>
+      <c r="W3" s="320"/>
+      <c r="X3" s="320"/>
       <c r="Y3" s="235"/>
-      <c r="Z3" s="321" t="s">
+      <c r="Z3" s="320" t="s">
         <v>0</v>
       </c>
-      <c r="AA3" s="321"/>
-      <c r="AB3" s="321"/>
-      <c r="AC3" s="321"/>
-      <c r="AD3" s="321" t="s">
+      <c r="AA3" s="320"/>
+      <c r="AB3" s="320"/>
+      <c r="AC3" s="320"/>
+      <c r="AD3" s="320" t="s">
         <v>1</v>
       </c>
-      <c r="AE3" s="321"/>
-      <c r="AF3" s="321"/>
+      <c r="AE3" s="320"/>
+      <c r="AF3" s="320"/>
       <c r="AG3" s="235"/>
     </row>
     <row r="4" spans="1:33" ht="36" x14ac:dyDescent="0.2">
-      <c r="A4" s="320"/>
+      <c r="A4" s="323"/>
       <c r="B4" s="236" t="s">
         <v>2</v>
       </c>
@@ -15796,17 +16011,17 @@
       </c>
     </row>
     <row r="14" spans="1:33" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="323" t="s">
+      <c r="A14" s="324" t="s">
         <v>54</v>
       </c>
-      <c r="B14" s="323"/>
-      <c r="C14" s="323"/>
-      <c r="D14" s="323"/>
-      <c r="E14" s="323"/>
-      <c r="F14" s="323"/>
-      <c r="G14" s="323"/>
-      <c r="H14" s="323"/>
-      <c r="I14" s="323"/>
+      <c r="B14" s="324"/>
+      <c r="C14" s="324"/>
+      <c r="D14" s="324"/>
+      <c r="E14" s="324"/>
+      <c r="F14" s="324"/>
+      <c r="G14" s="324"/>
+      <c r="H14" s="324"/>
+      <c r="I14" s="324"/>
     </row>
     <row r="15" spans="1:33" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="322" t="s">
@@ -15899,6 +16114,16 @@
     </row>
   </sheetData>
   <mergeCells count="21">
+    <mergeCell ref="Z2:AG2"/>
+    <mergeCell ref="Z3:AC3"/>
+    <mergeCell ref="AD3:AF3"/>
+    <mergeCell ref="A1:AG1"/>
+    <mergeCell ref="R2:Y2"/>
+    <mergeCell ref="R3:U3"/>
+    <mergeCell ref="V3:X3"/>
+    <mergeCell ref="J2:Q2"/>
+    <mergeCell ref="J3:M3"/>
+    <mergeCell ref="N3:P3"/>
     <mergeCell ref="A18:I18"/>
     <mergeCell ref="A19:I19"/>
     <mergeCell ref="A20:I20"/>
@@ -15910,16 +16135,6 @@
     <mergeCell ref="A16:I16"/>
     <mergeCell ref="A17:I17"/>
     <mergeCell ref="A14:I14"/>
-    <mergeCell ref="Z2:AG2"/>
-    <mergeCell ref="Z3:AC3"/>
-    <mergeCell ref="AD3:AF3"/>
-    <mergeCell ref="A1:AG1"/>
-    <mergeCell ref="R2:Y2"/>
-    <mergeCell ref="R3:U3"/>
-    <mergeCell ref="V3:X3"/>
-    <mergeCell ref="J2:Q2"/>
-    <mergeCell ref="J3:M3"/>
-    <mergeCell ref="N3:P3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="71" orientation="landscape" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
@@ -15967,41 +16182,41 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:33" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="324" t="s">
+      <c r="A1" s="325" t="s">
         <v>73</v>
       </c>
-      <c r="B1" s="324"/>
-      <c r="C1" s="324"/>
-      <c r="D1" s="324"/>
-      <c r="E1" s="324"/>
-      <c r="F1" s="324"/>
-      <c r="G1" s="324"/>
-      <c r="H1" s="324"/>
-      <c r="I1" s="324"/>
-      <c r="J1" s="324"/>
-      <c r="K1" s="324"/>
-      <c r="L1" s="324"/>
-      <c r="M1" s="324"/>
-      <c r="N1" s="324"/>
-      <c r="O1" s="324"/>
-      <c r="P1" s="324"/>
-      <c r="Q1" s="324"/>
-      <c r="R1" s="324"/>
-      <c r="S1" s="324"/>
-      <c r="T1" s="324"/>
-      <c r="U1" s="324"/>
-      <c r="V1" s="324"/>
-      <c r="W1" s="324"/>
-      <c r="X1" s="324"/>
-      <c r="Y1" s="324"/>
-      <c r="Z1" s="324"/>
-      <c r="AA1" s="324"/>
-      <c r="AB1" s="324"/>
-      <c r="AC1" s="324"/>
-      <c r="AD1" s="324"/>
-      <c r="AE1" s="324"/>
-      <c r="AF1" s="324"/>
-      <c r="AG1" s="324"/>
+      <c r="B1" s="325"/>
+      <c r="C1" s="325"/>
+      <c r="D1" s="325"/>
+      <c r="E1" s="325"/>
+      <c r="F1" s="325"/>
+      <c r="G1" s="325"/>
+      <c r="H1" s="325"/>
+      <c r="I1" s="325"/>
+      <c r="J1" s="325"/>
+      <c r="K1" s="325"/>
+      <c r="L1" s="325"/>
+      <c r="M1" s="325"/>
+      <c r="N1" s="325"/>
+      <c r="O1" s="325"/>
+      <c r="P1" s="325"/>
+      <c r="Q1" s="325"/>
+      <c r="R1" s="325"/>
+      <c r="S1" s="325"/>
+      <c r="T1" s="325"/>
+      <c r="U1" s="325"/>
+      <c r="V1" s="325"/>
+      <c r="W1" s="325"/>
+      <c r="X1" s="325"/>
+      <c r="Y1" s="325"/>
+      <c r="Z1" s="325"/>
+      <c r="AA1" s="325"/>
+      <c r="AB1" s="325"/>
+      <c r="AC1" s="325"/>
+      <c r="AD1" s="325"/>
+      <c r="AE1" s="325"/>
+      <c r="AF1" s="325"/>
+      <c r="AG1" s="325"/>
     </row>
     <row r="2" spans="1:33" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="175"/>
@@ -16024,7 +16239,7 @@
       <c r="N2" s="319"/>
       <c r="O2" s="319"/>
       <c r="P2" s="319"/>
-      <c r="Q2" s="325"/>
+      <c r="Q2" s="326"/>
       <c r="R2" s="319" t="s">
         <v>39</v>
       </c>
@@ -16034,7 +16249,7 @@
       <c r="V2" s="319"/>
       <c r="W2" s="319"/>
       <c r="X2" s="319"/>
-      <c r="Y2" s="325"/>
+      <c r="Y2" s="326"/>
       <c r="Z2" s="319" t="s">
         <v>40</v>
       </c>
@@ -16044,61 +16259,61 @@
       <c r="AD2" s="319"/>
       <c r="AE2" s="319"/>
       <c r="AF2" s="319"/>
-      <c r="AG2" s="325"/>
+      <c r="AG2" s="326"/>
     </row>
     <row r="3" spans="1:33" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A3" s="327"/>
-      <c r="B3" s="321" t="s">
+      <c r="A3" s="328"/>
+      <c r="B3" s="320" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="321"/>
-      <c r="D3" s="321"/>
-      <c r="E3" s="321"/>
-      <c r="F3" s="321" t="s">
+      <c r="C3" s="320"/>
+      <c r="D3" s="320"/>
+      <c r="E3" s="320"/>
+      <c r="F3" s="320" t="s">
         <v>1</v>
       </c>
-      <c r="G3" s="321"/>
-      <c r="H3" s="321"/>
+      <c r="G3" s="320"/>
+      <c r="H3" s="320"/>
       <c r="I3" s="235"/>
-      <c r="J3" s="326" t="s">
+      <c r="J3" s="327" t="s">
         <v>0</v>
       </c>
-      <c r="K3" s="326"/>
-      <c r="L3" s="326"/>
-      <c r="M3" s="326"/>
-      <c r="N3" s="326" t="s">
+      <c r="K3" s="327"/>
+      <c r="L3" s="327"/>
+      <c r="M3" s="327"/>
+      <c r="N3" s="327" t="s">
         <v>1</v>
       </c>
-      <c r="O3" s="326"/>
-      <c r="P3" s="326"/>
+      <c r="O3" s="327"/>
+      <c r="P3" s="327"/>
       <c r="Q3" s="254"/>
-      <c r="R3" s="326" t="s">
+      <c r="R3" s="327" t="s">
         <v>0</v>
       </c>
-      <c r="S3" s="326"/>
-      <c r="T3" s="326"/>
-      <c r="U3" s="326"/>
-      <c r="V3" s="326" t="s">
+      <c r="S3" s="327"/>
+      <c r="T3" s="327"/>
+      <c r="U3" s="327"/>
+      <c r="V3" s="327" t="s">
         <v>1</v>
       </c>
-      <c r="W3" s="326"/>
-      <c r="X3" s="326"/>
+      <c r="W3" s="327"/>
+      <c r="X3" s="327"/>
       <c r="Y3" s="254"/>
-      <c r="Z3" s="326" t="s">
+      <c r="Z3" s="327" t="s">
         <v>0</v>
       </c>
-      <c r="AA3" s="326"/>
-      <c r="AB3" s="326"/>
-      <c r="AC3" s="326"/>
-      <c r="AD3" s="326" t="s">
+      <c r="AA3" s="327"/>
+      <c r="AB3" s="327"/>
+      <c r="AC3" s="327"/>
+      <c r="AD3" s="327" t="s">
         <v>1</v>
       </c>
-      <c r="AE3" s="326"/>
-      <c r="AF3" s="326"/>
+      <c r="AE3" s="327"/>
+      <c r="AF3" s="327"/>
       <c r="AG3" s="254"/>
     </row>
     <row r="4" spans="1:33" ht="24" x14ac:dyDescent="0.2">
-      <c r="A4" s="327"/>
+      <c r="A4" s="328"/>
       <c r="B4" s="236" t="s">
         <v>2</v>
       </c>
@@ -16854,25 +17069,25 @@
       </c>
     </row>
     <row r="14" spans="1:33" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="323" t="s">
+      <c r="A14" s="324" t="s">
         <v>54</v>
       </c>
-      <c r="B14" s="323"/>
-      <c r="C14" s="323"/>
-      <c r="D14" s="323"/>
-      <c r="E14" s="323"/>
-      <c r="F14" s="323"/>
-      <c r="G14" s="323"/>
-      <c r="H14" s="323"/>
-      <c r="I14" s="323"/>
-      <c r="J14" s="323"/>
-      <c r="K14" s="323"/>
-      <c r="L14" s="323"/>
-      <c r="M14" s="323"/>
-      <c r="N14" s="323"/>
-      <c r="O14" s="323"/>
-      <c r="P14" s="323"/>
-      <c r="Q14" s="323"/>
+      <c r="B14" s="324"/>
+      <c r="C14" s="324"/>
+      <c r="D14" s="324"/>
+      <c r="E14" s="324"/>
+      <c r="F14" s="324"/>
+      <c r="G14" s="324"/>
+      <c r="H14" s="324"/>
+      <c r="I14" s="324"/>
+      <c r="J14" s="324"/>
+      <c r="K14" s="324"/>
+      <c r="L14" s="324"/>
+      <c r="M14" s="324"/>
+      <c r="N14" s="324"/>
+      <c r="O14" s="324"/>
+      <c r="P14" s="324"/>
+      <c r="Q14" s="324"/>
     </row>
     <row r="15" spans="1:33" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="322" t="s">
@@ -17021,13 +17236,6 @@
     </row>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="Z2:AG2"/>
-    <mergeCell ref="Z3:AC3"/>
-    <mergeCell ref="AD3:AF3"/>
-    <mergeCell ref="A1:AG1"/>
-    <mergeCell ref="R2:Y2"/>
-    <mergeCell ref="R3:U3"/>
-    <mergeCell ref="V3:X3"/>
     <mergeCell ref="A19:Q19"/>
     <mergeCell ref="A20:Q20"/>
     <mergeCell ref="J2:Q2"/>
@@ -17042,6 +17250,13 @@
     <mergeCell ref="A3:A4"/>
     <mergeCell ref="B3:E3"/>
     <mergeCell ref="F3:H3"/>
+    <mergeCell ref="Z2:AG2"/>
+    <mergeCell ref="Z3:AC3"/>
+    <mergeCell ref="AD3:AF3"/>
+    <mergeCell ref="A1:AG1"/>
+    <mergeCell ref="R2:Y2"/>
+    <mergeCell ref="R3:U3"/>
+    <mergeCell ref="V3:X3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="71" orientation="landscape" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
@@ -17089,41 +17304,41 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:33" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="324" t="s">
+      <c r="A1" s="325" t="s">
         <v>72</v>
       </c>
-      <c r="B1" s="324"/>
-      <c r="C1" s="324"/>
-      <c r="D1" s="324"/>
-      <c r="E1" s="324"/>
-      <c r="F1" s="324"/>
-      <c r="G1" s="324"/>
-      <c r="H1" s="324"/>
-      <c r="I1" s="324"/>
-      <c r="J1" s="324"/>
-      <c r="K1" s="324"/>
-      <c r="L1" s="324"/>
-      <c r="M1" s="324"/>
-      <c r="N1" s="324"/>
-      <c r="O1" s="324"/>
-      <c r="P1" s="324"/>
-      <c r="Q1" s="324"/>
-      <c r="R1" s="324"/>
-      <c r="S1" s="324"/>
-      <c r="T1" s="324"/>
-      <c r="U1" s="324"/>
-      <c r="V1" s="324"/>
-      <c r="W1" s="324"/>
-      <c r="X1" s="324"/>
-      <c r="Y1" s="324"/>
-      <c r="Z1" s="324"/>
-      <c r="AA1" s="324"/>
-      <c r="AB1" s="324"/>
-      <c r="AC1" s="324"/>
-      <c r="AD1" s="324"/>
-      <c r="AE1" s="324"/>
-      <c r="AF1" s="324"/>
-      <c r="AG1" s="324"/>
+      <c r="B1" s="325"/>
+      <c r="C1" s="325"/>
+      <c r="D1" s="325"/>
+      <c r="E1" s="325"/>
+      <c r="F1" s="325"/>
+      <c r="G1" s="325"/>
+      <c r="H1" s="325"/>
+      <c r="I1" s="325"/>
+      <c r="J1" s="325"/>
+      <c r="K1" s="325"/>
+      <c r="L1" s="325"/>
+      <c r="M1" s="325"/>
+      <c r="N1" s="325"/>
+      <c r="O1" s="325"/>
+      <c r="P1" s="325"/>
+      <c r="Q1" s="325"/>
+      <c r="R1" s="325"/>
+      <c r="S1" s="325"/>
+      <c r="T1" s="325"/>
+      <c r="U1" s="325"/>
+      <c r="V1" s="325"/>
+      <c r="W1" s="325"/>
+      <c r="X1" s="325"/>
+      <c r="Y1" s="325"/>
+      <c r="Z1" s="325"/>
+      <c r="AA1" s="325"/>
+      <c r="AB1" s="325"/>
+      <c r="AC1" s="325"/>
+      <c r="AD1" s="325"/>
+      <c r="AE1" s="325"/>
+      <c r="AF1" s="325"/>
+      <c r="AG1" s="325"/>
     </row>
     <row r="2" spans="1:33" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="175"/>
@@ -17156,7 +17371,7 @@
       <c r="V2" s="319"/>
       <c r="W2" s="319"/>
       <c r="X2" s="319"/>
-      <c r="Y2" s="325"/>
+      <c r="Y2" s="326"/>
       <c r="Z2" s="319" t="s">
         <v>40</v>
       </c>
@@ -17166,61 +17381,61 @@
       <c r="AD2" s="319"/>
       <c r="AE2" s="319"/>
       <c r="AF2" s="319"/>
-      <c r="AG2" s="325"/>
+      <c r="AG2" s="326"/>
     </row>
     <row r="3" spans="1:33" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A3" s="327"/>
-      <c r="B3" s="326" t="s">
+      <c r="A3" s="328"/>
+      <c r="B3" s="327" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="326"/>
-      <c r="D3" s="326"/>
-      <c r="E3" s="326"/>
-      <c r="F3" s="326" t="s">
+      <c r="C3" s="327"/>
+      <c r="D3" s="327"/>
+      <c r="E3" s="327"/>
+      <c r="F3" s="327" t="s">
         <v>1</v>
       </c>
-      <c r="G3" s="326"/>
-      <c r="H3" s="326"/>
+      <c r="G3" s="327"/>
+      <c r="H3" s="327"/>
       <c r="I3" s="122"/>
-      <c r="J3" s="326" t="s">
+      <c r="J3" s="327" t="s">
         <v>0</v>
       </c>
-      <c r="K3" s="326"/>
-      <c r="L3" s="326"/>
-      <c r="M3" s="326"/>
-      <c r="N3" s="326" t="s">
+      <c r="K3" s="327"/>
+      <c r="L3" s="327"/>
+      <c r="M3" s="327"/>
+      <c r="N3" s="327" t="s">
         <v>1</v>
       </c>
-      <c r="O3" s="326"/>
-      <c r="P3" s="326"/>
+      <c r="O3" s="327"/>
+      <c r="P3" s="327"/>
       <c r="Q3" s="122"/>
-      <c r="R3" s="326" t="s">
+      <c r="R3" s="327" t="s">
         <v>0</v>
       </c>
-      <c r="S3" s="326"/>
-      <c r="T3" s="326"/>
-      <c r="U3" s="326"/>
-      <c r="V3" s="326" t="s">
+      <c r="S3" s="327"/>
+      <c r="T3" s="327"/>
+      <c r="U3" s="327"/>
+      <c r="V3" s="327" t="s">
         <v>1</v>
       </c>
-      <c r="W3" s="326"/>
-      <c r="X3" s="326"/>
+      <c r="W3" s="327"/>
+      <c r="X3" s="327"/>
       <c r="Y3" s="218"/>
-      <c r="Z3" s="326" t="s">
+      <c r="Z3" s="327" t="s">
         <v>0</v>
       </c>
-      <c r="AA3" s="326"/>
-      <c r="AB3" s="326"/>
-      <c r="AC3" s="326"/>
-      <c r="AD3" s="326" t="s">
+      <c r="AA3" s="327"/>
+      <c r="AB3" s="327"/>
+      <c r="AC3" s="327"/>
+      <c r="AD3" s="327" t="s">
         <v>1</v>
       </c>
-      <c r="AE3" s="326"/>
-      <c r="AF3" s="326"/>
+      <c r="AE3" s="327"/>
+      <c r="AF3" s="327"/>
       <c r="AG3" s="218"/>
     </row>
     <row r="4" spans="1:33" ht="36" x14ac:dyDescent="0.2">
-      <c r="A4" s="327"/>
+      <c r="A4" s="328"/>
       <c r="B4" s="192" t="s">
         <v>2</v>
       </c>
@@ -17956,31 +18171,31 @@
       <c r="AG13" s="159"/>
     </row>
     <row r="14" spans="1:33" x14ac:dyDescent="0.2">
-      <c r="A14" s="323" t="s">
+      <c r="A14" s="324" t="s">
         <v>54</v>
       </c>
-      <c r="B14" s="323"/>
-      <c r="C14" s="323"/>
-      <c r="D14" s="323"/>
-      <c r="E14" s="323"/>
-      <c r="F14" s="323"/>
-      <c r="G14" s="323"/>
-      <c r="H14" s="323"/>
-      <c r="I14" s="323"/>
+      <c r="B14" s="324"/>
+      <c r="C14" s="324"/>
+      <c r="D14" s="324"/>
+      <c r="E14" s="324"/>
+      <c r="F14" s="324"/>
+      <c r="G14" s="324"/>
+      <c r="H14" s="324"/>
+      <c r="I14" s="324"/>
       <c r="T14" s="215"/>
     </row>
     <row r="15" spans="1:33" ht="46.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="328" t="s">
+      <c r="A15" s="329" t="s">
         <v>64</v>
       </c>
-      <c r="B15" s="328"/>
-      <c r="C15" s="328"/>
-      <c r="D15" s="328"/>
-      <c r="E15" s="328"/>
-      <c r="F15" s="328"/>
-      <c r="G15" s="328"/>
-      <c r="H15" s="328"/>
-      <c r="I15" s="328"/>
+      <c r="B15" s="329"/>
+      <c r="C15" s="329"/>
+      <c r="D15" s="329"/>
+      <c r="E15" s="329"/>
+      <c r="F15" s="329"/>
+      <c r="G15" s="329"/>
+      <c r="H15" s="329"/>
+      <c r="I15" s="329"/>
       <c r="T15" s="215"/>
     </row>
     <row r="16" spans="1:33" ht="54" customHeight="1" x14ac:dyDescent="0.2">
@@ -18139,6 +18354,11 @@
     </row>
   </sheetData>
   <mergeCells count="21">
+    <mergeCell ref="B3:E3"/>
+    <mergeCell ref="F3:H3"/>
+    <mergeCell ref="R2:Y2"/>
+    <mergeCell ref="R3:U3"/>
+    <mergeCell ref="V3:X3"/>
     <mergeCell ref="A1:AG1"/>
     <mergeCell ref="A19:I19"/>
     <mergeCell ref="A20:I20"/>
@@ -18155,11 +18375,6 @@
     <mergeCell ref="A16:I16"/>
     <mergeCell ref="B2:I2"/>
     <mergeCell ref="A3:A4"/>
-    <mergeCell ref="B3:E3"/>
-    <mergeCell ref="F3:H3"/>
-    <mergeCell ref="R2:Y2"/>
-    <mergeCell ref="R3:U3"/>
-    <mergeCell ref="V3:X3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="81" orientation="landscape" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
@@ -18202,41 +18417,41 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:33" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="324" t="s">
+      <c r="A1" s="325" t="s">
         <v>71</v>
       </c>
-      <c r="B1" s="324"/>
-      <c r="C1" s="324"/>
-      <c r="D1" s="324"/>
-      <c r="E1" s="324"/>
-      <c r="F1" s="324"/>
-      <c r="G1" s="324"/>
-      <c r="H1" s="324"/>
-      <c r="I1" s="324"/>
-      <c r="J1" s="324"/>
-      <c r="K1" s="324"/>
-      <c r="L1" s="324"/>
-      <c r="M1" s="324"/>
-      <c r="N1" s="324"/>
-      <c r="O1" s="324"/>
-      <c r="P1" s="324"/>
-      <c r="Q1" s="324"/>
-      <c r="R1" s="324"/>
-      <c r="S1" s="324"/>
-      <c r="T1" s="324"/>
-      <c r="U1" s="324"/>
-      <c r="V1" s="324"/>
-      <c r="W1" s="324"/>
-      <c r="X1" s="324"/>
-      <c r="Y1" s="324"/>
-      <c r="Z1" s="324"/>
-      <c r="AA1" s="324"/>
-      <c r="AB1" s="324"/>
-      <c r="AC1" s="324"/>
-      <c r="AD1" s="324"/>
-      <c r="AE1" s="324"/>
-      <c r="AF1" s="324"/>
-      <c r="AG1" s="324"/>
+      <c r="B1" s="325"/>
+      <c r="C1" s="325"/>
+      <c r="D1" s="325"/>
+      <c r="E1" s="325"/>
+      <c r="F1" s="325"/>
+      <c r="G1" s="325"/>
+      <c r="H1" s="325"/>
+      <c r="I1" s="325"/>
+      <c r="J1" s="325"/>
+      <c r="K1" s="325"/>
+      <c r="L1" s="325"/>
+      <c r="M1" s="325"/>
+      <c r="N1" s="325"/>
+      <c r="O1" s="325"/>
+      <c r="P1" s="325"/>
+      <c r="Q1" s="325"/>
+      <c r="R1" s="325"/>
+      <c r="S1" s="325"/>
+      <c r="T1" s="325"/>
+      <c r="U1" s="325"/>
+      <c r="V1" s="325"/>
+      <c r="W1" s="325"/>
+      <c r="X1" s="325"/>
+      <c r="Y1" s="325"/>
+      <c r="Z1" s="325"/>
+      <c r="AA1" s="325"/>
+      <c r="AB1" s="325"/>
+      <c r="AC1" s="325"/>
+      <c r="AD1" s="325"/>
+      <c r="AE1" s="325"/>
+      <c r="AF1" s="325"/>
+      <c r="AG1" s="325"/>
     </row>
     <row r="2" spans="1:33" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="175"/>
@@ -18269,8 +18484,8 @@
       <c r="V2" s="319"/>
       <c r="W2" s="319"/>
       <c r="X2" s="319"/>
-      <c r="Y2" s="325"/>
-      <c r="Z2" s="329" t="s">
+      <c r="Y2" s="326"/>
+      <c r="Z2" s="330" t="s">
         <v>40</v>
       </c>
       <c r="AA2" s="319"/>
@@ -18279,61 +18494,61 @@
       <c r="AD2" s="319"/>
       <c r="AE2" s="319"/>
       <c r="AF2" s="319"/>
-      <c r="AG2" s="325"/>
+      <c r="AG2" s="326"/>
     </row>
     <row r="3" spans="1:33" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A3" s="327"/>
-      <c r="B3" s="326" t="s">
+      <c r="A3" s="328"/>
+      <c r="B3" s="327" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="326"/>
-      <c r="D3" s="326"/>
-      <c r="E3" s="326"/>
-      <c r="F3" s="326" t="s">
+      <c r="C3" s="327"/>
+      <c r="D3" s="327"/>
+      <c r="E3" s="327"/>
+      <c r="F3" s="327" t="s">
         <v>1</v>
       </c>
-      <c r="G3" s="326"/>
-      <c r="H3" s="326"/>
+      <c r="G3" s="327"/>
+      <c r="H3" s="327"/>
       <c r="I3" s="122"/>
-      <c r="J3" s="326" t="s">
+      <c r="J3" s="327" t="s">
         <v>0</v>
       </c>
-      <c r="K3" s="326"/>
-      <c r="L3" s="326"/>
-      <c r="M3" s="326"/>
-      <c r="N3" s="326" t="s">
+      <c r="K3" s="327"/>
+      <c r="L3" s="327"/>
+      <c r="M3" s="327"/>
+      <c r="N3" s="327" t="s">
         <v>1</v>
       </c>
-      <c r="O3" s="326"/>
-      <c r="P3" s="326"/>
+      <c r="O3" s="327"/>
+      <c r="P3" s="327"/>
       <c r="Q3" s="122"/>
-      <c r="R3" s="326" t="s">
+      <c r="R3" s="327" t="s">
         <v>0</v>
       </c>
-      <c r="S3" s="326"/>
-      <c r="T3" s="326"/>
-      <c r="U3" s="326"/>
-      <c r="V3" s="326" t="s">
+      <c r="S3" s="327"/>
+      <c r="T3" s="327"/>
+      <c r="U3" s="327"/>
+      <c r="V3" s="327" t="s">
         <v>1</v>
       </c>
-      <c r="W3" s="326"/>
-      <c r="X3" s="326"/>
+      <c r="W3" s="327"/>
+      <c r="X3" s="327"/>
       <c r="Y3" s="170"/>
-      <c r="Z3" s="330" t="s">
+      <c r="Z3" s="331" t="s">
         <v>0</v>
       </c>
-      <c r="AA3" s="326"/>
-      <c r="AB3" s="326"/>
-      <c r="AC3" s="326"/>
-      <c r="AD3" s="326" t="s">
+      <c r="AA3" s="327"/>
+      <c r="AB3" s="327"/>
+      <c r="AC3" s="327"/>
+      <c r="AD3" s="327" t="s">
         <v>1</v>
       </c>
-      <c r="AE3" s="326"/>
-      <c r="AF3" s="326"/>
+      <c r="AE3" s="327"/>
+      <c r="AF3" s="327"/>
       <c r="AG3" s="170"/>
     </row>
     <row r="4" spans="1:33" ht="24" x14ac:dyDescent="0.2">
-      <c r="A4" s="327"/>
+      <c r="A4" s="328"/>
       <c r="B4" s="192" t="s">
         <v>2</v>
       </c>
@@ -19045,62 +19260,62 @@
       <c r="AG13" s="159"/>
     </row>
     <row r="14" spans="1:33" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="323" t="s">
+      <c r="A14" s="324" t="s">
         <v>54</v>
       </c>
-      <c r="B14" s="323"/>
-      <c r="C14" s="323"/>
-      <c r="D14" s="323"/>
-      <c r="E14" s="323"/>
-      <c r="F14" s="323"/>
-      <c r="G14" s="323"/>
-      <c r="H14" s="323"/>
-      <c r="I14" s="323"/>
-      <c r="J14" s="323"/>
-      <c r="K14" s="323"/>
-      <c r="L14" s="323"/>
-      <c r="M14" s="323"/>
-      <c r="N14" s="323"/>
-      <c r="O14" s="323"/>
-      <c r="P14" s="323"/>
-      <c r="Q14" s="323"/>
-      <c r="R14" s="323"/>
-      <c r="S14" s="323"/>
-      <c r="T14" s="323"/>
-      <c r="U14" s="323"/>
-      <c r="V14" s="323"/>
-      <c r="W14" s="323"/>
-      <c r="X14" s="323"/>
-      <c r="Y14" s="323"/>
+      <c r="B14" s="324"/>
+      <c r="C14" s="324"/>
+      <c r="D14" s="324"/>
+      <c r="E14" s="324"/>
+      <c r="F14" s="324"/>
+      <c r="G14" s="324"/>
+      <c r="H14" s="324"/>
+      <c r="I14" s="324"/>
+      <c r="J14" s="324"/>
+      <c r="K14" s="324"/>
+      <c r="L14" s="324"/>
+      <c r="M14" s="324"/>
+      <c r="N14" s="324"/>
+      <c r="O14" s="324"/>
+      <c r="P14" s="324"/>
+      <c r="Q14" s="324"/>
+      <c r="R14" s="324"/>
+      <c r="S14" s="324"/>
+      <c r="T14" s="324"/>
+      <c r="U14" s="324"/>
+      <c r="V14" s="324"/>
+      <c r="W14" s="324"/>
+      <c r="X14" s="324"/>
+      <c r="Y14" s="324"/>
     </row>
     <row r="15" spans="1:33" ht="81.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="328" t="s">
+      <c r="A15" s="329" t="s">
         <v>64</v>
       </c>
-      <c r="B15" s="328"/>
-      <c r="C15" s="328"/>
-      <c r="D15" s="328"/>
-      <c r="E15" s="328"/>
-      <c r="F15" s="328"/>
-      <c r="G15" s="328"/>
-      <c r="H15" s="328"/>
-      <c r="I15" s="328"/>
-      <c r="J15" s="328"/>
-      <c r="K15" s="328"/>
-      <c r="L15" s="328"/>
-      <c r="M15" s="328"/>
-      <c r="N15" s="328"/>
-      <c r="O15" s="328"/>
-      <c r="P15" s="328"/>
-      <c r="Q15" s="328"/>
-      <c r="R15" s="328"/>
-      <c r="S15" s="328"/>
-      <c r="T15" s="328"/>
-      <c r="U15" s="328"/>
-      <c r="V15" s="328"/>
-      <c r="W15" s="328"/>
-      <c r="X15" s="328"/>
-      <c r="Y15" s="328"/>
+      <c r="B15" s="329"/>
+      <c r="C15" s="329"/>
+      <c r="D15" s="329"/>
+      <c r="E15" s="329"/>
+      <c r="F15" s="329"/>
+      <c r="G15" s="329"/>
+      <c r="H15" s="329"/>
+      <c r="I15" s="329"/>
+      <c r="J15" s="329"/>
+      <c r="K15" s="329"/>
+      <c r="L15" s="329"/>
+      <c r="M15" s="329"/>
+      <c r="N15" s="329"/>
+      <c r="O15" s="329"/>
+      <c r="P15" s="329"/>
+      <c r="Q15" s="329"/>
+      <c r="R15" s="329"/>
+      <c r="S15" s="329"/>
+      <c r="T15" s="329"/>
+      <c r="U15" s="329"/>
+      <c r="V15" s="329"/>
+      <c r="W15" s="329"/>
+      <c r="X15" s="329"/>
+      <c r="Y15" s="329"/>
     </row>
     <row r="16" spans="1:33" ht="37.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="322" t="s">
@@ -19419,6 +19634,12 @@
     </row>
   </sheetData>
   <mergeCells count="22">
+    <mergeCell ref="Z2:AG2"/>
+    <mergeCell ref="Z3:AC3"/>
+    <mergeCell ref="AD3:AF3"/>
+    <mergeCell ref="R3:U3"/>
+    <mergeCell ref="V3:X3"/>
+    <mergeCell ref="R2:Y2"/>
     <mergeCell ref="A1:AG1"/>
     <mergeCell ref="A21:Y21"/>
     <mergeCell ref="A15:Y15"/>
@@ -19435,12 +19656,6 @@
     <mergeCell ref="J2:Q2"/>
     <mergeCell ref="J3:M3"/>
     <mergeCell ref="N3:P3"/>
-    <mergeCell ref="Z2:AG2"/>
-    <mergeCell ref="Z3:AC3"/>
-    <mergeCell ref="AD3:AF3"/>
-    <mergeCell ref="R3:U3"/>
-    <mergeCell ref="V3:X3"/>
-    <mergeCell ref="R2:Y2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -19476,54 +19691,54 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:33" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="324" t="s">
+      <c r="A1" s="325" t="s">
         <v>69</v>
       </c>
-      <c r="B1" s="324"/>
-      <c r="C1" s="324"/>
-      <c r="D1" s="324"/>
-      <c r="E1" s="324"/>
-      <c r="F1" s="324"/>
-      <c r="G1" s="324"/>
-      <c r="H1" s="324"/>
-      <c r="I1" s="324"/>
-      <c r="J1" s="324"/>
-      <c r="K1" s="324"/>
-      <c r="L1" s="324"/>
-      <c r="M1" s="324"/>
-      <c r="N1" s="324"/>
-      <c r="O1" s="324"/>
-      <c r="P1" s="324"/>
-      <c r="Q1" s="324"/>
-      <c r="R1" s="324"/>
-      <c r="S1" s="324"/>
-      <c r="T1" s="324"/>
-      <c r="U1" s="324"/>
-      <c r="V1" s="324"/>
-      <c r="W1" s="324"/>
-      <c r="X1" s="324"/>
-      <c r="Y1" s="324"/>
-      <c r="Z1" s="324"/>
-      <c r="AA1" s="324"/>
-      <c r="AB1" s="324"/>
-      <c r="AC1" s="324"/>
-      <c r="AD1" s="324"/>
-      <c r="AE1" s="324"/>
-      <c r="AF1" s="324"/>
-      <c r="AG1" s="324"/>
+      <c r="B1" s="325"/>
+      <c r="C1" s="325"/>
+      <c r="D1" s="325"/>
+      <c r="E1" s="325"/>
+      <c r="F1" s="325"/>
+      <c r="G1" s="325"/>
+      <c r="H1" s="325"/>
+      <c r="I1" s="325"/>
+      <c r="J1" s="325"/>
+      <c r="K1" s="325"/>
+      <c r="L1" s="325"/>
+      <c r="M1" s="325"/>
+      <c r="N1" s="325"/>
+      <c r="O1" s="325"/>
+      <c r="P1" s="325"/>
+      <c r="Q1" s="325"/>
+      <c r="R1" s="325"/>
+      <c r="S1" s="325"/>
+      <c r="T1" s="325"/>
+      <c r="U1" s="325"/>
+      <c r="V1" s="325"/>
+      <c r="W1" s="325"/>
+      <c r="X1" s="325"/>
+      <c r="Y1" s="325"/>
+      <c r="Z1" s="325"/>
+      <c r="AA1" s="325"/>
+      <c r="AB1" s="325"/>
+      <c r="AC1" s="325"/>
+      <c r="AD1" s="325"/>
+      <c r="AE1" s="325"/>
+      <c r="AF1" s="325"/>
+      <c r="AG1" s="325"/>
     </row>
     <row r="2" spans="1:33" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="175"/>
-      <c r="B2" s="331" t="s">
+      <c r="B2" s="332" t="s">
         <v>50</v>
       </c>
-      <c r="C2" s="331"/>
-      <c r="D2" s="331"/>
-      <c r="E2" s="331"/>
-      <c r="F2" s="331"/>
-      <c r="G2" s="331"/>
-      <c r="H2" s="331"/>
-      <c r="I2" s="331"/>
+      <c r="C2" s="332"/>
+      <c r="D2" s="332"/>
+      <c r="E2" s="332"/>
+      <c r="F2" s="332"/>
+      <c r="G2" s="332"/>
+      <c r="H2" s="332"/>
+      <c r="I2" s="332"/>
       <c r="J2" s="319" t="s">
         <v>49</v>
       </c>
@@ -19556,58 +19771,58 @@
       <c r="AG2" s="319"/>
     </row>
     <row r="3" spans="1:33" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A3" s="327"/>
-      <c r="B3" s="326" t="s">
+      <c r="A3" s="328"/>
+      <c r="B3" s="327" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="326"/>
-      <c r="D3" s="326"/>
-      <c r="E3" s="326"/>
-      <c r="F3" s="326" t="s">
+      <c r="C3" s="327"/>
+      <c r="D3" s="327"/>
+      <c r="E3" s="327"/>
+      <c r="F3" s="327" t="s">
         <v>1</v>
       </c>
-      <c r="G3" s="326"/>
-      <c r="H3" s="326"/>
-      <c r="I3" s="326"/>
-      <c r="J3" s="326" t="s">
+      <c r="G3" s="327"/>
+      <c r="H3" s="327"/>
+      <c r="I3" s="327"/>
+      <c r="J3" s="327" t="s">
         <v>0</v>
       </c>
-      <c r="K3" s="326"/>
-      <c r="L3" s="326"/>
-      <c r="M3" s="326"/>
-      <c r="N3" s="326" t="s">
+      <c r="K3" s="327"/>
+      <c r="L3" s="327"/>
+      <c r="M3" s="327"/>
+      <c r="N3" s="327" t="s">
         <v>1</v>
       </c>
-      <c r="O3" s="326"/>
-      <c r="P3" s="326"/>
+      <c r="O3" s="327"/>
+      <c r="P3" s="327"/>
       <c r="Q3" s="122"/>
-      <c r="R3" s="326" t="s">
+      <c r="R3" s="327" t="s">
         <v>0</v>
       </c>
-      <c r="S3" s="326"/>
-      <c r="T3" s="326"/>
-      <c r="U3" s="326"/>
-      <c r="V3" s="326" t="s">
+      <c r="S3" s="327"/>
+      <c r="T3" s="327"/>
+      <c r="U3" s="327"/>
+      <c r="V3" s="327" t="s">
         <v>1</v>
       </c>
-      <c r="W3" s="326"/>
-      <c r="X3" s="326"/>
+      <c r="W3" s="327"/>
+      <c r="X3" s="327"/>
       <c r="Y3" s="194"/>
-      <c r="Z3" s="326" t="s">
+      <c r="Z3" s="327" t="s">
         <v>0</v>
       </c>
-      <c r="AA3" s="326"/>
-      <c r="AB3" s="326"/>
-      <c r="AC3" s="326"/>
-      <c r="AD3" s="326" t="s">
+      <c r="AA3" s="327"/>
+      <c r="AB3" s="327"/>
+      <c r="AC3" s="327"/>
+      <c r="AD3" s="327" t="s">
         <v>1</v>
       </c>
-      <c r="AE3" s="326"/>
-      <c r="AF3" s="326"/>
+      <c r="AE3" s="327"/>
+      <c r="AF3" s="327"/>
       <c r="AG3" s="122"/>
     </row>
     <row r="4" spans="1:33" ht="24" x14ac:dyDescent="0.2">
-      <c r="A4" s="327"/>
+      <c r="A4" s="328"/>
       <c r="B4" s="78" t="s">
         <v>2</v>
       </c>
@@ -20355,78 +20570,78 @@
       <c r="AG13" s="64"/>
     </row>
     <row r="14" spans="1:33" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="323" t="s">
+      <c r="A14" s="324" t="s">
         <v>54</v>
       </c>
-      <c r="B14" s="323"/>
-      <c r="C14" s="323"/>
-      <c r="D14" s="323"/>
-      <c r="E14" s="323"/>
-      <c r="F14" s="323"/>
-      <c r="G14" s="323"/>
-      <c r="H14" s="323"/>
-      <c r="I14" s="323"/>
-      <c r="J14" s="323"/>
-      <c r="K14" s="323"/>
-      <c r="L14" s="323"/>
-      <c r="M14" s="323"/>
-      <c r="N14" s="323"/>
-      <c r="O14" s="323"/>
-      <c r="P14" s="323"/>
-      <c r="Q14" s="323"/>
-      <c r="R14" s="323"/>
-      <c r="S14" s="323"/>
-      <c r="T14" s="323"/>
-      <c r="U14" s="323"/>
-      <c r="V14" s="323"/>
-      <c r="W14" s="323"/>
-      <c r="X14" s="323"/>
-      <c r="Y14" s="323"/>
-      <c r="Z14" s="323"/>
-      <c r="AA14" s="323"/>
-      <c r="AB14" s="323"/>
-      <c r="AC14" s="323"/>
-      <c r="AD14" s="323"/>
-      <c r="AE14" s="323"/>
-      <c r="AF14" s="323"/>
-      <c r="AG14" s="323"/>
+      <c r="B14" s="324"/>
+      <c r="C14" s="324"/>
+      <c r="D14" s="324"/>
+      <c r="E14" s="324"/>
+      <c r="F14" s="324"/>
+      <c r="G14" s="324"/>
+      <c r="H14" s="324"/>
+      <c r="I14" s="324"/>
+      <c r="J14" s="324"/>
+      <c r="K14" s="324"/>
+      <c r="L14" s="324"/>
+      <c r="M14" s="324"/>
+      <c r="N14" s="324"/>
+      <c r="O14" s="324"/>
+      <c r="P14" s="324"/>
+      <c r="Q14" s="324"/>
+      <c r="R14" s="324"/>
+      <c r="S14" s="324"/>
+      <c r="T14" s="324"/>
+      <c r="U14" s="324"/>
+      <c r="V14" s="324"/>
+      <c r="W14" s="324"/>
+      <c r="X14" s="324"/>
+      <c r="Y14" s="324"/>
+      <c r="Z14" s="324"/>
+      <c r="AA14" s="324"/>
+      <c r="AB14" s="324"/>
+      <c r="AC14" s="324"/>
+      <c r="AD14" s="324"/>
+      <c r="AE14" s="324"/>
+      <c r="AF14" s="324"/>
+      <c r="AG14" s="324"/>
     </row>
     <row r="15" spans="1:33" ht="81.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="328" t="s">
+      <c r="A15" s="329" t="s">
         <v>64</v>
       </c>
-      <c r="B15" s="328"/>
-      <c r="C15" s="328"/>
-      <c r="D15" s="328"/>
-      <c r="E15" s="328"/>
-      <c r="F15" s="328"/>
-      <c r="G15" s="328"/>
-      <c r="H15" s="328"/>
-      <c r="I15" s="328"/>
-      <c r="J15" s="328"/>
-      <c r="K15" s="328"/>
-      <c r="L15" s="328"/>
-      <c r="M15" s="328"/>
-      <c r="N15" s="328"/>
-      <c r="O15" s="328"/>
-      <c r="P15" s="328"/>
-      <c r="Q15" s="328"/>
-      <c r="R15" s="328"/>
-      <c r="S15" s="328"/>
-      <c r="T15" s="328"/>
-      <c r="U15" s="328"/>
-      <c r="V15" s="328"/>
-      <c r="W15" s="328"/>
-      <c r="X15" s="328"/>
-      <c r="Y15" s="328"/>
-      <c r="Z15" s="328"/>
-      <c r="AA15" s="328"/>
-      <c r="AB15" s="328"/>
-      <c r="AC15" s="328"/>
-      <c r="AD15" s="328"/>
-      <c r="AE15" s="328"/>
-      <c r="AF15" s="328"/>
-      <c r="AG15" s="328"/>
+      <c r="B15" s="329"/>
+      <c r="C15" s="329"/>
+      <c r="D15" s="329"/>
+      <c r="E15" s="329"/>
+      <c r="F15" s="329"/>
+      <c r="G15" s="329"/>
+      <c r="H15" s="329"/>
+      <c r="I15" s="329"/>
+      <c r="J15" s="329"/>
+      <c r="K15" s="329"/>
+      <c r="L15" s="329"/>
+      <c r="M15" s="329"/>
+      <c r="N15" s="329"/>
+      <c r="O15" s="329"/>
+      <c r="P15" s="329"/>
+      <c r="Q15" s="329"/>
+      <c r="R15" s="329"/>
+      <c r="S15" s="329"/>
+      <c r="T15" s="329"/>
+      <c r="U15" s="329"/>
+      <c r="V15" s="329"/>
+      <c r="W15" s="329"/>
+      <c r="X15" s="329"/>
+      <c r="Y15" s="329"/>
+      <c r="Z15" s="329"/>
+      <c r="AA15" s="329"/>
+      <c r="AB15" s="329"/>
+      <c r="AC15" s="329"/>
+      <c r="AD15" s="329"/>
+      <c r="AE15" s="329"/>
+      <c r="AF15" s="329"/>
+      <c r="AG15" s="329"/>
     </row>
     <row r="16" spans="1:33" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="322" t="s">
@@ -20769,12 +20984,6 @@
     </row>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="A20:AG20"/>
-    <mergeCell ref="A15:AG15"/>
-    <mergeCell ref="A16:AG16"/>
-    <mergeCell ref="A17:AG17"/>
-    <mergeCell ref="A18:AG18"/>
-    <mergeCell ref="A19:AG19"/>
     <mergeCell ref="Z3:AC3"/>
     <mergeCell ref="AD3:AF3"/>
     <mergeCell ref="Z2:AG2"/>
@@ -20790,6 +20999,12 @@
     <mergeCell ref="J2:Q2"/>
     <mergeCell ref="J3:M3"/>
     <mergeCell ref="N3:P3"/>
+    <mergeCell ref="A20:AG20"/>
+    <mergeCell ref="A15:AG15"/>
+    <mergeCell ref="A16:AG16"/>
+    <mergeCell ref="A17:AG17"/>
+    <mergeCell ref="A18:AG18"/>
+    <mergeCell ref="A19:AG19"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
